--- a/NN/reports/model_comparison.xlsx
+++ b/NN/reports/model_comparison.xlsx
@@ -14,10 +14,10 @@
     <sheet name="Metadata" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Model Comparison'!$A$1:$M$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Model Comparison'!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Best by Target'!$A$1:$M$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Overall Average'!$A$1:$G$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Fold Metrics'!$A$1:$G$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Overall Average'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Fold Metrics'!$A$1:$G$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Metadata'!$A$1:$G$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -553,28 +553,28 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.5145843769405422</v>
+        <v>0.4765076752689186</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2.324408554265008</v>
+        <v>2.411560166509476</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1.469392900104812</v>
+        <v>1.534844103509903</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9.156155169255126</v>
+        <v>9.698517973516919</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.05547054150310106</v>
+        <v>0.0532260007112829</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.3326911062311049</v>
+        <v>0.3044464880315454</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.1440550240776139</v>
+        <v>0.1294739352122044</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.8165757686407461</v>
+        <v>0.8251772995582216</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>5</v>
@@ -598,28 +598,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4693202744333728</v>
+        <v>0.4408515721769954</v>
       </c>
       <c r="F3" t="n">
-        <v>2.431822390292165</v>
+        <v>2.496458653689449</v>
       </c>
       <c r="G3" t="n">
-        <v>1.540545760434302</v>
+        <v>1.596568687890219</v>
       </c>
       <c r="H3" t="n">
-        <v>9.728131021221682</v>
+        <v>10.10424737583744</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08802979849040111</v>
+        <v>0.08929621776651257</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4147953125467811</v>
+        <v>0.4197133664981815</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1536577359258706</v>
+        <v>0.1659924308846498</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6294274558814169</v>
+        <v>0.6679998713349482</v>
       </c>
       <c r="M3" t="n">
         <v>5</v>
@@ -643,28 +643,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.4528727854530306</v>
+        <v>0.4388202209456302</v>
       </c>
       <c r="F4" t="n">
-        <v>2.455369244103912</v>
+        <v>2.493266719528956</v>
       </c>
       <c r="G4" t="n">
-        <v>1.616266828169435</v>
+        <v>1.625587415166397</v>
       </c>
       <c r="H4" t="n">
-        <v>10.40245184834743</v>
+        <v>10.5175527143969</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07588795418503885</v>
+        <v>0.06998022441478449</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2419776457187243</v>
+        <v>0.3108560338679105</v>
       </c>
       <c r="K4" t="n">
-        <v>0.09816228546697167</v>
+        <v>0.1447888080838037</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5789204230913501</v>
+        <v>0.876721359005583</v>
       </c>
       <c r="M4" t="n">
         <v>5</v>
@@ -688,28 +688,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.4041066691564266</v>
+        <v>0.4093377555016319</v>
       </c>
       <c r="F5" t="n">
-        <v>2.56125358609114</v>
+        <v>2.55086904063175</v>
       </c>
       <c r="G5" t="n">
-        <v>1.722720249009499</v>
+        <v>1.766342309897531</v>
       </c>
       <c r="H5" t="n">
-        <v>11.07068904226662</v>
+        <v>11.53482859524611</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06974896813083979</v>
+        <v>0.07758407243283573</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1879798155985191</v>
+        <v>0.2350186167615563</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1141711970306861</v>
+        <v>0.107096557123969</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8095514614440562</v>
+        <v>0.8681846242125181</v>
       </c>
       <c r="M5" t="n">
         <v>5</v>
@@ -733,80 +733,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.4012945541335625</v>
+        <v>0.3345282627238162</v>
       </c>
       <c r="F6" t="n">
-        <v>2.56466168751983</v>
+        <v>2.701491283093353</v>
       </c>
       <c r="G6" t="n">
-        <v>1.604388690086644</v>
+        <v>1.714295529055329</v>
       </c>
       <c r="H6" t="n">
-        <v>10.21126081730861</v>
+        <v>11.09118254822936</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1112647802768699</v>
+        <v>0.130292270355815</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3211165637487183</v>
+        <v>0.3274730188216585</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1183153972470814</v>
+        <v>0.1411293970243854</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7512904023338809</v>
+        <v>1.097335947280984</v>
       </c>
       <c r="M6" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>white_total_points</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ANN</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>-1240.066511860409</v>
-      </c>
-      <c r="F7" t="n">
-        <v>50.09792275680392</v>
-      </c>
-      <c r="G7" t="n">
-        <v>8.189043064103631</v>
-      </c>
-      <c r="H7" t="n">
-        <v>54.86519755537294</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2767.148055614202</v>
-      </c>
-      <c r="J7" t="n">
-        <v>99.81596596206644</v>
-      </c>
-      <c r="K7" t="n">
-        <v>12.80964650386224</v>
-      </c>
-      <c r="L7" t="n">
-        <v>88.90338285873041</v>
-      </c>
-      <c r="M7" t="n">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M7"/>
+  <autoFilter ref="A1:M6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -824,12 +779,12 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
@@ -920,28 +875,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.5145843769405422</v>
+        <v>0.4765076752689186</v>
       </c>
       <c r="F2" t="n">
-        <v>2.324408554265008</v>
+        <v>2.411560166509476</v>
       </c>
       <c r="G2" t="n">
-        <v>1.469392900104812</v>
+        <v>1.534844103509903</v>
       </c>
       <c r="H2" t="n">
-        <v>9.156155169255126</v>
+        <v>9.698517973516919</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05547054150310106</v>
+        <v>0.0532260007112829</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3326911062311049</v>
+        <v>0.3044464880315454</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1440550240776139</v>
+        <v>0.1294739352122044</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8165757686407461</v>
+        <v>0.8251772995582216</v>
       </c>
       <c r="M2" t="n">
         <v>5</v>
@@ -959,7 +914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1018,16 +973,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5145843769405422</v>
+        <v>0.4765076752689186</v>
       </c>
       <c r="D2" t="n">
-        <v>2.324408554265008</v>
+        <v>2.411560166509476</v>
       </c>
       <c r="E2" t="n">
-        <v>1.469392900104812</v>
+        <v>1.534844103509903</v>
       </c>
       <c r="F2" t="n">
-        <v>9.156155169255126</v>
+        <v>9.698517973516919</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -1043,16 +998,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.4693202744333728</v>
+        <v>0.4408515721769954</v>
       </c>
       <c r="D3" t="n">
-        <v>2.431822390292165</v>
+        <v>2.496458653689449</v>
       </c>
       <c r="E3" t="n">
-        <v>1.540545760434302</v>
+        <v>1.596568687890219</v>
       </c>
       <c r="F3" t="n">
-        <v>9.728131021221682</v>
+        <v>10.10424737583744</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -1068,16 +1023,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.4528727854530306</v>
+        <v>0.4388202209456302</v>
       </c>
       <c r="D4" t="n">
-        <v>2.455369244103912</v>
+        <v>2.493266719528956</v>
       </c>
       <c r="E4" t="n">
-        <v>1.616266828169435</v>
+        <v>1.625587415166397</v>
       </c>
       <c r="F4" t="n">
-        <v>10.40245184834743</v>
+        <v>10.5175527143969</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -1093,16 +1048,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.4041066691564266</v>
+        <v>0.4093377555016319</v>
       </c>
       <c r="D5" t="n">
-        <v>2.56125358609114</v>
+        <v>2.55086904063175</v>
       </c>
       <c r="E5" t="n">
-        <v>1.722720249009499</v>
+        <v>1.766342309897531</v>
       </c>
       <c r="F5" t="n">
-        <v>11.07068904226662</v>
+        <v>11.53482859524611</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -1118,48 +1073,23 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.4012945541335625</v>
+        <v>0.3345282627238162</v>
       </c>
       <c r="D6" t="n">
-        <v>2.56466168751983</v>
+        <v>2.701491283093353</v>
       </c>
       <c r="E6" t="n">
-        <v>1.604388690086644</v>
+        <v>1.714295529055329</v>
       </c>
       <c r="F6" t="n">
-        <v>10.21126081730861</v>
+        <v>11.09118254822936</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ANN</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>-1240.066511860409</v>
-      </c>
-      <c r="D7" t="n">
-        <v>50.09792275680392</v>
-      </c>
-      <c r="E7" t="n">
-        <v>8.189043064103631</v>
-      </c>
-      <c r="F7" t="n">
-        <v>54.86519755537294</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G7"/>
+  <autoFilter ref="A1:G6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1170,13 +1100,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
@@ -1234,16 +1164,16 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4015377454027587</v>
+        <v>0.3661937960470624</v>
       </c>
       <c r="E2" t="n">
-        <v>2.247102901284053</v>
+        <v>2.312505749809305</v>
       </c>
       <c r="F2" t="n">
-        <v>1.47646540084388</v>
+        <v>1.545371187191988</v>
       </c>
       <c r="G2" t="n">
-        <v>9.922465910465334</v>
+        <v>10.40183769171498</v>
       </c>
     </row>
     <row r="3">
@@ -1261,16 +1191,16 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0.526154792462501</v>
+        <v>0.4921235294267304</v>
       </c>
       <c r="E3" t="n">
-        <v>2.398171389668895</v>
+        <v>2.48279588934721</v>
       </c>
       <c r="F3" t="n">
-        <v>1.530081645569618</v>
+        <v>1.610253412237118</v>
       </c>
       <c r="G3" t="n">
-        <v>9.410586514416016</v>
+        <v>9.956950329181975</v>
       </c>
     </row>
     <row r="4">
@@ -1288,16 +1218,16 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5904034131806324</v>
+        <v>0.5609748691944558</v>
       </c>
       <c r="E4" t="n">
-        <v>1.940899140532581</v>
+        <v>2.009414323653141</v>
       </c>
       <c r="F4" t="n">
-        <v>1.39386434599156</v>
+        <v>1.438499018169184</v>
       </c>
       <c r="G4" t="n">
-        <v>9.249174606340071</v>
+        <v>9.550552752519167</v>
       </c>
     </row>
     <row r="5">
@@ -1315,16 +1245,16 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4492266175267952</v>
+        <v>0.440357589338596</v>
       </c>
       <c r="E5" t="n">
-        <v>2.50326219417127</v>
+        <v>2.523336547052147</v>
       </c>
       <c r="F5" t="n">
-        <v>1.502428874734609</v>
+        <v>1.516464962158538</v>
       </c>
       <c r="G5" t="n">
-        <v>9.309695478537982</v>
+        <v>9.503858645705247</v>
       </c>
     </row>
     <row r="6">
@@ -1342,16 +1272,16 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3792788035941768</v>
+        <v>0.3446080768781326</v>
       </c>
       <c r="E6" t="n">
-        <v>3.069676325804024</v>
+        <v>3.154240758585444</v>
       </c>
       <c r="F6" t="n">
-        <v>1.799888535031846</v>
+        <v>1.872254859694268</v>
       </c>
       <c r="G6" t="n">
-        <v>10.748732596349</v>
+        <v>11.10803746006581</v>
       </c>
     </row>
     <row r="7">
@@ -1369,16 +1299,16 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4921050851862888</v>
+        <v>0.417362163119355</v>
       </c>
       <c r="E7" t="n">
-        <v>2.070100882792117</v>
+        <v>2.217195153270039</v>
       </c>
       <c r="F7" t="n">
-        <v>1.348342616033752</v>
+        <v>1.461699314345989</v>
       </c>
       <c r="G7" t="n">
-        <v>8.850431925043637</v>
+        <v>9.669592453056524</v>
       </c>
     </row>
     <row r="8">
@@ -1396,16 +1326,16 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6022918301486295</v>
+        <v>0.5494097054474665</v>
       </c>
       <c r="E8" t="n">
-        <v>2.197071686983065</v>
+        <v>2.338583535539986</v>
       </c>
       <c r="F8" t="n">
-        <v>1.422623839662446</v>
+        <v>1.507964135021097</v>
       </c>
       <c r="G8" t="n">
-        <v>9.136907946025026</v>
+        <v>9.786398256157359</v>
       </c>
     </row>
     <row r="9">
@@ -1423,16 +1353,16 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5324335348160025</v>
+        <v>0.5119710041894012</v>
       </c>
       <c r="E9" t="n">
-        <v>2.073702641042575</v>
+        <v>2.118593405923864</v>
       </c>
       <c r="F9" t="n">
-        <v>1.430940295358649</v>
+        <v>1.453856962025314</v>
       </c>
       <c r="G9" t="n">
-        <v>8.993695474295889</v>
+        <v>9.175101638224193</v>
       </c>
     </row>
     <row r="10">
@@ -1450,16 +1380,16 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4860936110184394</v>
+        <v>0.4569070746174353</v>
       </c>
       <c r="E10" t="n">
-        <v>2.418031070610127</v>
+        <v>2.485747099407418</v>
       </c>
       <c r="F10" t="n">
-        <v>1.425195541401273</v>
+        <v>1.487437515923568</v>
       </c>
       <c r="G10" t="n">
-        <v>8.298017367358991</v>
+        <v>8.850636789832791</v>
       </c>
     </row>
     <row r="11">
@@ -1477,16 +1407,16 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4599978235333505</v>
+        <v>0.4468884289709351</v>
       </c>
       <c r="E11" t="n">
-        <v>2.863136489897156</v>
+        <v>2.897681638406072</v>
       </c>
       <c r="F11" t="n">
-        <v>1.719862208067939</v>
+        <v>1.763262590233544</v>
       </c>
       <c r="G11" t="n">
-        <v>10.50172313355208</v>
+        <v>11.01086073031373</v>
       </c>
     </row>
     <row r="12">
@@ -1504,16 +1434,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3391971885866912</v>
+        <v>0.2466817044568479</v>
       </c>
       <c r="E12" t="n">
-        <v>2.361242107523141</v>
+        <v>2.521121846931162</v>
       </c>
       <c r="F12" t="n">
-        <v>1.519681488743311</v>
+        <v>1.726586229042917</v>
       </c>
       <c r="G12" t="n">
-        <v>10.2263668811902</v>
+        <v>12.02141174942526</v>
       </c>
     </row>
     <row r="13">
@@ -1531,16 +1461,16 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5613640609441286</v>
+        <v>0.4854850393527227</v>
       </c>
       <c r="E13" t="n">
-        <v>2.307353187896521</v>
+        <v>2.498969611270043</v>
       </c>
       <c r="F13" t="n">
-        <v>1.529611498274475</v>
+        <v>1.638364736570187</v>
       </c>
       <c r="G13" t="n">
-        <v>10.01857004224986</v>
+        <v>10.67477652803051</v>
       </c>
     </row>
     <row r="14">
@@ -1558,16 +1488,16 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2796470998064836</v>
+        <v>0.1862107655493713</v>
       </c>
       <c r="E14" t="n">
-        <v>2.57393430260522</v>
+        <v>2.735777499606052</v>
       </c>
       <c r="F14" t="n">
-        <v>1.620011617322511</v>
+        <v>1.645973095079011</v>
       </c>
       <c r="G14" t="n">
-        <v>9.92482676321551</v>
+        <v>10.02780513329258</v>
       </c>
     </row>
     <row r="15">
@@ -1585,16 +1515,16 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4629454224329047</v>
+        <v>0.453849294222548</v>
       </c>
       <c r="E15" t="n">
-        <v>2.471889654535175</v>
+        <v>2.492735037933065</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5485793393129</v>
+        <v>1.606526294331642</v>
       </c>
       <c r="G15" t="n">
-        <v>9.435626916834176</v>
+        <v>10.24880078443368</v>
       </c>
     </row>
     <row r="16">
@@ -1612,16 +1542,16 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3633189988976043</v>
+        <v>0.3004145100375909</v>
       </c>
       <c r="E16" t="n">
-        <v>3.108889185039096</v>
+        <v>3.258852419726442</v>
       </c>
       <c r="F16" t="n">
-        <v>1.804059506780023</v>
+        <v>1.954027290252886</v>
       </c>
       <c r="G16" t="n">
-        <v>11.45091348305329</v>
+        <v>12.48311854596476</v>
       </c>
     </row>
     <row r="17">
@@ -1639,16 +1569,16 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3363215730070706</v>
+        <v>0.3274929375142605</v>
       </c>
       <c r="E17" t="n">
-        <v>2.366374238823536</v>
+        <v>2.382061681844692</v>
       </c>
       <c r="F17" t="n">
-        <v>1.591060840532472</v>
+        <v>1.750001852170618</v>
       </c>
       <c r="G17" t="n">
-        <v>10.57986722665282</v>
+        <v>11.94566602545771</v>
       </c>
     </row>
     <row r="18">
@@ -1666,16 +1596,16 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4638000330871673</v>
+        <v>0.4513700056554267</v>
       </c>
       <c r="E18" t="n">
-        <v>2.55108754638635</v>
+        <v>2.580487412482213</v>
       </c>
       <c r="F18" t="n">
-        <v>1.776180592898495</v>
+        <v>1.800309644768467</v>
       </c>
       <c r="G18" t="n">
-        <v>11.66768665646218</v>
+        <v>11.94550649964226</v>
       </c>
     </row>
     <row r="19">
@@ -1693,16 +1623,16 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3203747054320681</v>
+        <v>0.3325680303804825</v>
       </c>
       <c r="E19" t="n">
-        <v>2.500112608568134</v>
+        <v>2.477583532976815</v>
       </c>
       <c r="F19" t="n">
-        <v>1.78514571015618</v>
+        <v>1.817210665169984</v>
       </c>
       <c r="G19" t="n">
-        <v>11.74069759972516</v>
+        <v>12.12646373167338</v>
       </c>
     </row>
     <row r="20">
@@ -1720,16 +1650,16 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4439062366013358</v>
+        <v>0.5058556117916981</v>
       </c>
       <c r="E20" t="n">
-        <v>2.515323688149471</v>
+        <v>2.371083249075643</v>
       </c>
       <c r="F20" t="n">
-        <v>1.612440432698072</v>
+        <v>1.591516402701223</v>
       </c>
       <c r="G20" t="n">
-        <v>9.884461686310214</v>
+        <v>10.0130830799387</v>
       </c>
     </row>
     <row r="21">
@@ -1747,16 +1677,16 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4561307976544915</v>
+        <v>0.4294021921662918</v>
       </c>
       <c r="E21" t="n">
-        <v>2.873369848528209</v>
+        <v>2.94312932677939</v>
       </c>
       <c r="F21" t="n">
-        <v>1.848773668762279</v>
+        <v>1.872672984677363</v>
       </c>
       <c r="G21" t="n">
-        <v>11.48073204218273</v>
+        <v>11.64342363951849</v>
       </c>
     </row>
     <row r="22">
@@ -1774,16 +1704,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3372961985579841</v>
+        <v>0.3554489229980099</v>
       </c>
       <c r="E22" t="n">
-        <v>2.364636065600208</v>
+        <v>2.332025244907385</v>
       </c>
       <c r="F22" t="n">
-        <v>1.610978207194598</v>
+        <v>1.6303785324707</v>
       </c>
       <c r="G22" t="n">
-        <v>10.82854740139946</v>
+        <v>11.16083627093857</v>
       </c>
     </row>
     <row r="23">
@@ -1801,16 +1731,16 @@
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5493056142525183</v>
+        <v>0.534076328776136</v>
       </c>
       <c r="E23" t="n">
-        <v>2.338853638891928</v>
+        <v>2.378041114165839</v>
       </c>
       <c r="F23" t="n">
-        <v>1.625921075521627</v>
+        <v>1.613236220192948</v>
       </c>
       <c r="G23" t="n">
-        <v>10.6114096453814</v>
+        <v>10.64391890958581</v>
       </c>
     </row>
     <row r="24">
@@ -1828,16 +1758,16 @@
         <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4486943163963046</v>
+        <v>0.4370769714601126</v>
       </c>
       <c r="E24" t="n">
-        <v>2.251754493728487</v>
+        <v>2.275355766200653</v>
       </c>
       <c r="F24" t="n">
-        <v>1.54304571975113</v>
+        <v>1.54779774834892</v>
       </c>
       <c r="G24" t="n">
-        <v>10.19277402867325</v>
+        <v>10.04911682515822</v>
       </c>
     </row>
     <row r="25">
@@ -1855,16 +1785,16 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4712146815302456</v>
+        <v>0.4756419418281129</v>
       </c>
       <c r="E25" t="n">
-        <v>2.452785459113523</v>
+        <v>2.442495891233774</v>
       </c>
       <c r="F25" t="n">
-        <v>1.526819039469361</v>
+        <v>1.475926425884253</v>
       </c>
       <c r="G25" t="n">
-        <v>9.489429275775372</v>
+        <v>9.276078665180689</v>
       </c>
     </row>
     <row r="26">
@@ -1882,155 +1812,20 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4578531165281005</v>
+        <v>0.3918569396657796</v>
       </c>
       <c r="E26" t="n">
-        <v>2.868816563185415</v>
+        <v>3.038415581137128</v>
       </c>
       <c r="F26" t="n">
-        <v>1.774570098910459</v>
+        <v>1.860598148935164</v>
       </c>
       <c r="G26" t="n">
-        <v>10.89009889050769</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>white_total_points</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>ANN</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="n">
-        <v>-6190.085439247944</v>
-      </c>
-      <c r="E27" t="n">
-        <v>228.5535529867034</v>
-      </c>
-      <c r="F27" t="n">
-        <v>31.08492251341857</v>
-      </c>
-      <c r="G27" t="n">
-        <v>213.7727705458932</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>white_total_points</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>ANN</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>2</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.3038851827565814</v>
-      </c>
-      <c r="E28" t="n">
-        <v>2.906714722242037</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1.856949741266951</v>
-      </c>
-      <c r="G28" t="n">
-        <v>10.78180750393283</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>white_total_points</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>ANN</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>3</v>
-      </c>
-      <c r="D29" t="n">
-        <v>-0.1853806614197888</v>
-      </c>
-      <c r="E29" t="n">
-        <v>3.301822495748634</v>
-      </c>
-      <c r="F29" t="n">
-        <v>2.047338595420499</v>
-      </c>
-      <c r="G29" t="n">
-        <v>12.84068010041299</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>white_total_points</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>ANN</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>4</v>
-      </c>
-      <c r="D30" t="n">
-        <v>-10.0109049765689</v>
-      </c>
-      <c r="E30" t="n">
-        <v>11.19261011980602</v>
-      </c>
-      <c r="F30" t="n">
-        <v>3.000869104786284</v>
-      </c>
-      <c r="G30" t="n">
-        <v>19.93645082659454</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>white_total_points</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>ANN</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>5</v>
-      </c>
-      <c r="D31" t="n">
-        <v>-0.3547195988713336</v>
-      </c>
-      <c r="E31" t="n">
-        <v>4.534913459519537</v>
-      </c>
-      <c r="F31" t="n">
-        <v>2.955135365625855</v>
-      </c>
-      <c r="G31" t="n">
-        <v>16.99427880003117</v>
+        <v>11.45781290112121</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G31"/>
+  <autoFilter ref="A1:G26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2093,7 +1888,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-11 05:10:23 UTC</t>
+          <t>2026-06-14 22:03:48 UTC</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/NN/reports/model_comparison.xlsx
+++ b/NN/reports/model_comparison.xlsx
@@ -553,28 +553,28 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.4765076752689186</v>
+        <v>0.4790210056139861</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2.411560166509476</v>
+        <v>2.408221793130511</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1.534844103509903</v>
+        <v>1.530190702876651</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9.698517973516919</v>
+        <v>9.633515023990958</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.0532260007112829</v>
+        <v>0.05816015557226745</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.3044464880315454</v>
+        <v>0.3367691529534158</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.1294739352122044</v>
+        <v>0.1268875576118172</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.8251772995582216</v>
+        <v>0.7968637774497822</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>5</v>
@@ -594,32 +594,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4408515721769954</v>
+        <v>0.4494194581064545</v>
       </c>
       <c r="F3" t="n">
-        <v>2.496458653689449</v>
+        <v>2.473026092383978</v>
       </c>
       <c r="G3" t="n">
-        <v>1.596568687890219</v>
+        <v>1.627142652419954</v>
       </c>
       <c r="H3" t="n">
-        <v>10.10424737583744</v>
+        <v>10.53220501748255</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08929621776651257</v>
+        <v>0.04540235017535934</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4197133664981815</v>
+        <v>0.2913784362516137</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1659924308846498</v>
+        <v>0.1304491283798283</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6679998713349482</v>
+        <v>0.7267719132411676</v>
       </c>
       <c r="M3" t="n">
         <v>5</v>
@@ -639,32 +639,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.4388202209456302</v>
+        <v>0.4428214973398167</v>
       </c>
       <c r="F4" t="n">
-        <v>2.493266719528956</v>
+        <v>2.49239265448724</v>
       </c>
       <c r="G4" t="n">
-        <v>1.625587415166397</v>
+        <v>1.597195050210214</v>
       </c>
       <c r="H4" t="n">
-        <v>10.5175527143969</v>
+        <v>10.12535111598181</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06998022441478449</v>
+        <v>0.08424149689667475</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3108560338679105</v>
+        <v>0.410036728257862</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1447888080838037</v>
+        <v>0.1628969802222278</v>
       </c>
       <c r="L4" t="n">
-        <v>0.876721359005583</v>
+        <v>0.6505444953908815</v>
       </c>
       <c r="M4" t="n">
         <v>5</v>
@@ -688,28 +688,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.4093377555016319</v>
+        <v>0.398732133764691</v>
       </c>
       <c r="F5" t="n">
-        <v>2.55086904063175</v>
+        <v>2.572498618429586</v>
       </c>
       <c r="G5" t="n">
-        <v>1.766342309897531</v>
+        <v>1.753634376995053</v>
       </c>
       <c r="H5" t="n">
-        <v>11.53482859524611</v>
+        <v>11.40348575662846</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07758407243283573</v>
+        <v>0.0855659426221056</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2350186167615563</v>
+        <v>0.2447622569044677</v>
       </c>
       <c r="K5" t="n">
-        <v>0.107096557123969</v>
+        <v>0.1321470279833912</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8681846242125181</v>
+        <v>0.9374848334087262</v>
       </c>
       <c r="M5" t="n">
         <v>5</v>
@@ -733,28 +733,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.3345282627238162</v>
+        <v>0.3892029208226518</v>
       </c>
       <c r="F6" t="n">
-        <v>2.701491283093353</v>
+        <v>2.597452979392447</v>
       </c>
       <c r="G6" t="n">
-        <v>1.714295529055329</v>
+        <v>1.693708568646101</v>
       </c>
       <c r="H6" t="n">
-        <v>11.09118254822936</v>
+        <v>11.00674175245207</v>
       </c>
       <c r="I6" t="n">
-        <v>0.130292270355815</v>
+        <v>0.1071285434871453</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3274730188216585</v>
+        <v>0.3772216342269124</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1411293970243854</v>
+        <v>0.1722307423769188</v>
       </c>
       <c r="L6" t="n">
-        <v>1.097335947280984</v>
+        <v>1.156614700802941</v>
       </c>
       <c r="M6" t="n">
         <v>5</v>
@@ -779,11 +779,11 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.4765076752689186</v>
+        <v>0.4790210056139861</v>
       </c>
       <c r="F2" t="n">
-        <v>2.411560166509476</v>
+        <v>2.408221793130511</v>
       </c>
       <c r="G2" t="n">
-        <v>1.534844103509903</v>
+        <v>1.530190702876651</v>
       </c>
       <c r="H2" t="n">
-        <v>9.698517973516919</v>
+        <v>9.633515023990958</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0532260007112829</v>
+        <v>0.05816015557226745</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3044464880315454</v>
+        <v>0.3367691529534158</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1294739352122044</v>
+        <v>0.1268875576118172</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8251772995582216</v>
+        <v>0.7968637774497822</v>
       </c>
       <c r="M2" t="n">
         <v>5</v>
@@ -973,16 +973,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4765076752689186</v>
+        <v>0.4790210056139861</v>
       </c>
       <c r="D2" t="n">
-        <v>2.411560166509476</v>
+        <v>2.408221793130511</v>
       </c>
       <c r="E2" t="n">
-        <v>1.534844103509903</v>
+        <v>1.530190702876651</v>
       </c>
       <c r="F2" t="n">
-        <v>9.698517973516919</v>
+        <v>9.633515023990958</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -994,20 +994,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.4408515721769954</v>
+        <v>0.4494194581064545</v>
       </c>
       <c r="D3" t="n">
-        <v>2.496458653689449</v>
+        <v>2.473026092383978</v>
       </c>
       <c r="E3" t="n">
-        <v>1.596568687890219</v>
+        <v>1.627142652419954</v>
       </c>
       <c r="F3" t="n">
-        <v>10.10424737583744</v>
+        <v>10.53220501748255</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -1019,20 +1019,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.4388202209456302</v>
+        <v>0.4428214973398167</v>
       </c>
       <c r="D4" t="n">
-        <v>2.493266719528956</v>
+        <v>2.49239265448724</v>
       </c>
       <c r="E4" t="n">
-        <v>1.625587415166397</v>
+        <v>1.597195050210214</v>
       </c>
       <c r="F4" t="n">
-        <v>10.5175527143969</v>
+        <v>10.12535111598181</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -1048,16 +1048,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.4093377555016319</v>
+        <v>0.398732133764691</v>
       </c>
       <c r="D5" t="n">
-        <v>2.55086904063175</v>
+        <v>2.572498618429586</v>
       </c>
       <c r="E5" t="n">
-        <v>1.766342309897531</v>
+        <v>1.753634376995053</v>
       </c>
       <c r="F5" t="n">
-        <v>11.53482859524611</v>
+        <v>11.40348575662846</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.3345282627238162</v>
+        <v>0.3892029208226518</v>
       </c>
       <c r="D6" t="n">
-        <v>2.701491283093353</v>
+        <v>2.597452979392447</v>
       </c>
       <c r="E6" t="n">
-        <v>1.714295529055329</v>
+        <v>1.693708568646101</v>
       </c>
       <c r="F6" t="n">
-        <v>11.09118254822936</v>
+        <v>11.00674175245207</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -1164,16 +1164,16 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3661937960470624</v>
+        <v>0.3702880735716577</v>
       </c>
       <c r="E2" t="n">
-        <v>2.312505749809305</v>
+        <v>2.305024456381418</v>
       </c>
       <c r="F2" t="n">
-        <v>1.545371187191988</v>
+        <v>1.539169348223839</v>
       </c>
       <c r="G2" t="n">
-        <v>10.40183769171498</v>
+        <v>10.34390825287467</v>
       </c>
     </row>
     <row r="3">
@@ -1191,16 +1191,16 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4921235294267304</v>
+        <v>0.4775121928822613</v>
       </c>
       <c r="E3" t="n">
-        <v>2.48279588934721</v>
+        <v>2.518257008536305</v>
       </c>
       <c r="F3" t="n">
-        <v>1.610253412237118</v>
+        <v>1.632227553575185</v>
       </c>
       <c r="G3" t="n">
-        <v>9.956950329181975</v>
+        <v>10.07094822888103</v>
       </c>
     </row>
     <row r="4">
@@ -1218,16 +1218,16 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5609748691944558</v>
+        <v>0.5643773005380752</v>
       </c>
       <c r="E4" t="n">
-        <v>2.009414323653141</v>
+        <v>2.001612728930465</v>
       </c>
       <c r="F4" t="n">
-        <v>1.438499018169184</v>
+        <v>1.429332677404348</v>
       </c>
       <c r="G4" t="n">
-        <v>9.550552752519167</v>
+        <v>9.538782294363644</v>
       </c>
     </row>
     <row r="5">
@@ -1245,16 +1245,16 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.440357589338596</v>
+        <v>0.4436394517952583</v>
       </c>
       <c r="E5" t="n">
-        <v>2.523336547052147</v>
+        <v>2.515926976409569</v>
       </c>
       <c r="F5" t="n">
-        <v>1.516464962158538</v>
+        <v>1.526555461791202</v>
       </c>
       <c r="G5" t="n">
-        <v>9.503858645705247</v>
+        <v>9.559118485251197</v>
       </c>
     </row>
     <row r="6">
@@ -1272,16 +1272,16 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3446080768781326</v>
+        <v>0.3582904679118309</v>
       </c>
       <c r="E6" t="n">
-        <v>3.154240758585444</v>
+        <v>3.121142102178442</v>
       </c>
       <c r="F6" t="n">
-        <v>1.872254859694268</v>
+        <v>1.858690210056495</v>
       </c>
       <c r="G6" t="n">
-        <v>11.10803746006581</v>
+        <v>11.1139983185385</v>
       </c>
     </row>
     <row r="7">
@@ -1299,16 +1299,16 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.417362163119355</v>
+        <v>0.4307982338134093</v>
       </c>
       <c r="E7" t="n">
-        <v>2.217195153270039</v>
+        <v>2.191480939823528</v>
       </c>
       <c r="F7" t="n">
-        <v>1.461699314345989</v>
+        <v>1.463787737341771</v>
       </c>
       <c r="G7" t="n">
-        <v>9.669592453056524</v>
+        <v>9.597159016181552</v>
       </c>
     </row>
     <row r="8">
@@ -1326,16 +1326,16 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5494097054474665</v>
+        <v>0.5445341047434713</v>
       </c>
       <c r="E8" t="n">
-        <v>2.338583535539986</v>
+        <v>2.351201785046227</v>
       </c>
       <c r="F8" t="n">
-        <v>1.507964135021097</v>
+        <v>1.509909614225436</v>
       </c>
       <c r="G8" t="n">
-        <v>9.786398256157359</v>
+        <v>9.841628232468222</v>
       </c>
     </row>
     <row r="9">
@@ -1353,16 +1353,16 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5119710041894012</v>
+        <v>0.5405513660113825</v>
       </c>
       <c r="E9" t="n">
-        <v>2.118593405923864</v>
+        <v>2.055622135032329</v>
       </c>
       <c r="F9" t="n">
-        <v>1.453856962025314</v>
+        <v>1.427372808251288</v>
       </c>
       <c r="G9" t="n">
-        <v>9.175101638224193</v>
+        <v>9.077482397235464</v>
       </c>
     </row>
     <row r="10">
@@ -1380,16 +1380,16 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4569070746174353</v>
+        <v>0.4428260349503099</v>
       </c>
       <c r="E10" t="n">
-        <v>2.485747099407418</v>
+        <v>2.51776548735817</v>
       </c>
       <c r="F10" t="n">
-        <v>1.487437515923568</v>
+        <v>1.5003340552017</v>
       </c>
       <c r="G10" t="n">
-        <v>8.850636789832791</v>
+        <v>8.797954199321607</v>
       </c>
     </row>
     <row r="11">
@@ -1407,16 +1407,16 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4468884289709351</v>
+        <v>0.4363952885513575</v>
       </c>
       <c r="E11" t="n">
-        <v>2.897681638406072</v>
+        <v>2.925038618392301</v>
       </c>
       <c r="F11" t="n">
-        <v>1.763262590233544</v>
+        <v>1.749549299363057</v>
       </c>
       <c r="G11" t="n">
-        <v>11.01086073031373</v>
+        <v>10.85335127474795</v>
       </c>
     </row>
     <row r="12">
@@ -1434,16 +1434,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2466817044568479</v>
+        <v>0.3325701574480541</v>
       </c>
       <c r="E12" t="n">
-        <v>2.521121846931162</v>
+        <v>2.373052732147749</v>
       </c>
       <c r="F12" t="n">
-        <v>1.726586229042917</v>
+        <v>1.703520238897469</v>
       </c>
       <c r="G12" t="n">
-        <v>12.02141174942526</v>
+        <v>11.81203055985724</v>
       </c>
     </row>
     <row r="13">
@@ -1461,16 +1461,16 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4854850393527227</v>
+        <v>0.5196382969760538</v>
       </c>
       <c r="E13" t="n">
-        <v>2.498969611270043</v>
+        <v>2.414605353444562</v>
       </c>
       <c r="F13" t="n">
-        <v>1.638364736570187</v>
+        <v>1.601538847353268</v>
       </c>
       <c r="G13" t="n">
-        <v>10.67477652803051</v>
+        <v>10.53391292861681</v>
       </c>
     </row>
     <row r="14">
@@ -1488,16 +1488,16 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1862107655493713</v>
+        <v>0.3049577158718695</v>
       </c>
       <c r="E14" t="n">
-        <v>2.735777499606052</v>
+        <v>2.528310547593204</v>
       </c>
       <c r="F14" t="n">
-        <v>1.645973095079011</v>
+        <v>1.646172383314446</v>
       </c>
       <c r="G14" t="n">
-        <v>10.02780513329258</v>
+        <v>10.26310526409532</v>
       </c>
     </row>
     <row r="15">
@@ -1515,16 +1515,16 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0.453849294222548</v>
+        <v>0.4906886019535568</v>
       </c>
       <c r="E15" t="n">
-        <v>2.492735037933065</v>
+        <v>2.407196627738349</v>
       </c>
       <c r="F15" t="n">
-        <v>1.606526294331642</v>
+        <v>1.535758577334653</v>
       </c>
       <c r="G15" t="n">
-        <v>10.24880078443368</v>
+        <v>9.826428706301396</v>
       </c>
     </row>
     <row r="16">
@@ -1542,16 +1542,16 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3004145100375909</v>
+        <v>0.2981598318637253</v>
       </c>
       <c r="E16" t="n">
-        <v>3.258852419726442</v>
+        <v>3.264099636038372</v>
       </c>
       <c r="F16" t="n">
-        <v>1.954027290252886</v>
+        <v>1.98155279633067</v>
       </c>
       <c r="G16" t="n">
-        <v>12.48311854596476</v>
+        <v>12.59823130338961</v>
       </c>
     </row>
     <row r="17">
@@ -1569,16 +1569,16 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3274929375142605</v>
+        <v>0.3081414786113043</v>
       </c>
       <c r="E17" t="n">
-        <v>2.382061681844692</v>
+        <v>2.416090654380424</v>
       </c>
       <c r="F17" t="n">
-        <v>1.750001852170618</v>
+        <v>1.696929526684865</v>
       </c>
       <c r="G17" t="n">
-        <v>11.94566602545771</v>
+        <v>11.52572390200825</v>
       </c>
     </row>
     <row r="18">
@@ -1596,16 +1596,16 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4513700056554267</v>
+        <v>0.4215032241787866</v>
       </c>
       <c r="E18" t="n">
-        <v>2.580487412482213</v>
+        <v>2.649796015146564</v>
       </c>
       <c r="F18" t="n">
-        <v>1.800309644768467</v>
+        <v>1.806030218274586</v>
       </c>
       <c r="G18" t="n">
-        <v>11.94550649964226</v>
+        <v>12.01320004918785</v>
       </c>
     </row>
     <row r="19">
@@ -1623,16 +1623,16 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3325680303804825</v>
+        <v>0.3230005748246274</v>
       </c>
       <c r="E19" t="n">
-        <v>2.477583532976815</v>
+        <v>2.495278089620727</v>
       </c>
       <c r="F19" t="n">
-        <v>1.817210665169984</v>
+        <v>1.824995743571001</v>
       </c>
       <c r="G19" t="n">
-        <v>12.12646373167338</v>
+        <v>11.97058085844532</v>
       </c>
     </row>
     <row r="20">
@@ -1650,16 +1650,16 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5058556117916981</v>
+        <v>0.5180587272081942</v>
       </c>
       <c r="E20" t="n">
-        <v>2.371083249075643</v>
+        <v>2.341622749386803</v>
       </c>
       <c r="F20" t="n">
-        <v>1.591516402701223</v>
+        <v>1.551956288002059</v>
       </c>
       <c r="G20" t="n">
-        <v>10.0130830799387</v>
+        <v>9.763139485247104</v>
       </c>
     </row>
     <row r="21">
@@ -1677,16 +1677,16 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4294021921662918</v>
+        <v>0.4229566640005425</v>
       </c>
       <c r="E21" t="n">
-        <v>2.94312932677939</v>
+        <v>2.959705583613412</v>
       </c>
       <c r="F21" t="n">
-        <v>1.872672984677363</v>
+        <v>1.888260108442756</v>
       </c>
       <c r="G21" t="n">
-        <v>11.64342363951849</v>
+        <v>11.7447844882538</v>
       </c>
     </row>
     <row r="22">
@@ -1704,16 +1704,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3554489229980099</v>
+        <v>0.3867277772682304</v>
       </c>
       <c r="E22" t="n">
-        <v>2.332025244907385</v>
+        <v>2.274737176713528</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6303785324707</v>
+        <v>1.601427891765505</v>
       </c>
       <c r="G22" t="n">
-        <v>11.16083627093857</v>
+        <v>10.90088843762073</v>
       </c>
     </row>
     <row r="23">
@@ -1731,16 +1731,16 @@
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>0.534076328776136</v>
+        <v>0.5059497043389669</v>
       </c>
       <c r="E23" t="n">
-        <v>2.378041114165839</v>
+        <v>2.448767501883184</v>
       </c>
       <c r="F23" t="n">
-        <v>1.613236220192948</v>
+        <v>1.648459500166954</v>
       </c>
       <c r="G23" t="n">
-        <v>10.64391890958581</v>
+        <v>10.86184108108688</v>
       </c>
     </row>
     <row r="24">
@@ -1758,16 +1758,16 @@
         <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4370769714601126</v>
+        <v>0.4662751269819717</v>
       </c>
       <c r="E24" t="n">
-        <v>2.275355766200653</v>
+        <v>2.215560044727363</v>
       </c>
       <c r="F24" t="n">
-        <v>1.54779774834892</v>
+        <v>1.522872488193711</v>
       </c>
       <c r="G24" t="n">
-        <v>10.04911682515822</v>
+        <v>9.959266879544298</v>
       </c>
     </row>
     <row r="25">
@@ -1785,16 +1785,16 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4756419418281129</v>
+        <v>0.4637989869586896</v>
       </c>
       <c r="E25" t="n">
-        <v>2.442495891233774</v>
+        <v>2.469924531787909</v>
       </c>
       <c r="F25" t="n">
-        <v>1.475926425884253</v>
+        <v>1.523085402045285</v>
       </c>
       <c r="G25" t="n">
-        <v>9.276078665180689</v>
+        <v>9.59427611816731</v>
       </c>
     </row>
     <row r="26">
@@ -1812,16 +1812,16 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3918569396657796</v>
+        <v>0.4243456949844134</v>
       </c>
       <c r="E26" t="n">
-        <v>3.038415581137128</v>
+        <v>2.956141206807906</v>
       </c>
       <c r="F26" t="n">
-        <v>1.860598148935164</v>
+        <v>1.839867979928314</v>
       </c>
       <c r="G26" t="n">
-        <v>11.45781290112121</v>
+        <v>11.34475257099355</v>
       </c>
     </row>
   </sheetData>
@@ -1888,7 +1888,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-14 22:03:48 UTC</t>
+          <t>2026-06-15 07:33:39 UTC</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/NN/reports/model_comparison.xlsx
+++ b/NN/reports/model_comparison.xlsx
@@ -457,7 +457,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -553,28 +553,28 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.4790210056139861</v>
+        <v>0.5145843769405423</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2.408221793130511</v>
+        <v>2.324408554265008</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1.530190702876651</v>
+        <v>1.469392900104812</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9.633515023990958</v>
+        <v>9.156155169255126</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.05816015557226745</v>
+        <v>0.05547054150310088</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.3367691529534158</v>
+        <v>0.3326911062311046</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.1268875576118172</v>
+        <v>0.144055024077614</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.7968637774497822</v>
+        <v>0.8165757686407459</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>5</v>
@@ -594,32 +594,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4494194581064545</v>
+        <v>0.4693202744333728</v>
       </c>
       <c r="F3" t="n">
-        <v>2.473026092383978</v>
+        <v>2.431822390292165</v>
       </c>
       <c r="G3" t="n">
-        <v>1.627142652419954</v>
+        <v>1.540545760434303</v>
       </c>
       <c r="H3" t="n">
-        <v>10.53220501748255</v>
+        <v>9.728131021221682</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04540235017535934</v>
+        <v>0.08802979849040111</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2913784362516137</v>
+        <v>0.4147953125467814</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1304491283798283</v>
+        <v>0.1536577359258706</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7267719132411676</v>
+        <v>0.6294274558814178</v>
       </c>
       <c r="M3" t="n">
         <v>5</v>
@@ -639,32 +639,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.4428214973398167</v>
+        <v>0.4528727854530306</v>
       </c>
       <c r="F4" t="n">
-        <v>2.49239265448724</v>
+        <v>2.455369244103912</v>
       </c>
       <c r="G4" t="n">
-        <v>1.597195050210214</v>
+        <v>1.616266828169435</v>
       </c>
       <c r="H4" t="n">
-        <v>10.12535111598181</v>
+        <v>10.40245184834743</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08424149689667475</v>
+        <v>0.07588795418503885</v>
       </c>
       <c r="J4" t="n">
-        <v>0.410036728257862</v>
+        <v>0.2419776457187243</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1628969802222278</v>
+        <v>0.09816228546697167</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6505444953908815</v>
+        <v>0.5789204230913501</v>
       </c>
       <c r="M4" t="n">
         <v>5</v>
@@ -688,28 +688,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.398732133764691</v>
+        <v>0.4041066691564266</v>
       </c>
       <c r="F5" t="n">
-        <v>2.572498618429586</v>
+        <v>2.56125358609114</v>
       </c>
       <c r="G5" t="n">
-        <v>1.753634376995053</v>
+        <v>1.722720249009499</v>
       </c>
       <c r="H5" t="n">
-        <v>11.40348575662846</v>
+        <v>11.07068904226662</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0855659426221056</v>
+        <v>0.06974896813083979</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2447622569044677</v>
+        <v>0.1879798155985191</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1321470279833912</v>
+        <v>0.1141711970306861</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9374848334087262</v>
+        <v>0.8095514614440562</v>
       </c>
       <c r="M5" t="n">
         <v>5</v>
@@ -733,28 +733,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.3892029208226518</v>
+        <v>0.4012945541335625</v>
       </c>
       <c r="F6" t="n">
-        <v>2.597452979392447</v>
+        <v>2.56466168751983</v>
       </c>
       <c r="G6" t="n">
-        <v>1.693708568646101</v>
+        <v>1.604388690086644</v>
       </c>
       <c r="H6" t="n">
-        <v>11.00674175245207</v>
+        <v>10.21126081730861</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1071285434871453</v>
+        <v>0.1112647802768699</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3772216342269124</v>
+        <v>0.3211165637487183</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1722307423769188</v>
+        <v>0.1183153972470814</v>
       </c>
       <c r="L6" t="n">
-        <v>1.156614700802941</v>
+        <v>0.7512904023338809</v>
       </c>
       <c r="M6" t="n">
         <v>5</v>
@@ -780,7 +780,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.4790210056139861</v>
+        <v>0.5145843769405423</v>
       </c>
       <c r="F2" t="n">
-        <v>2.408221793130511</v>
+        <v>2.324408554265008</v>
       </c>
       <c r="G2" t="n">
-        <v>1.530190702876651</v>
+        <v>1.469392900104812</v>
       </c>
       <c r="H2" t="n">
-        <v>9.633515023990958</v>
+        <v>9.156155169255126</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05816015557226745</v>
+        <v>0.05547054150310088</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3367691529534158</v>
+        <v>0.3326911062311046</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1268875576118172</v>
+        <v>0.144055024077614</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7968637774497822</v>
+        <v>0.8165757686407459</v>
       </c>
       <c r="M2" t="n">
         <v>5</v>
@@ -919,7 +919,7 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -973,16 +973,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4790210056139861</v>
+        <v>0.5145843769405423</v>
       </c>
       <c r="D2" t="n">
-        <v>2.408221793130511</v>
+        <v>2.324408554265008</v>
       </c>
       <c r="E2" t="n">
-        <v>1.530190702876651</v>
+        <v>1.469392900104812</v>
       </c>
       <c r="F2" t="n">
-        <v>9.633515023990958</v>
+        <v>9.156155169255126</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -994,20 +994,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.4494194581064545</v>
+        <v>0.4693202744333728</v>
       </c>
       <c r="D3" t="n">
-        <v>2.473026092383978</v>
+        <v>2.431822390292165</v>
       </c>
       <c r="E3" t="n">
-        <v>1.627142652419954</v>
+        <v>1.540545760434303</v>
       </c>
       <c r="F3" t="n">
-        <v>10.53220501748255</v>
+        <v>9.728131021221682</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -1019,20 +1019,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.4428214973398167</v>
+        <v>0.4528727854530306</v>
       </c>
       <c r="D4" t="n">
-        <v>2.49239265448724</v>
+        <v>2.455369244103912</v>
       </c>
       <c r="E4" t="n">
-        <v>1.597195050210214</v>
+        <v>1.616266828169435</v>
       </c>
       <c r="F4" t="n">
-        <v>10.12535111598181</v>
+        <v>10.40245184834743</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -1048,16 +1048,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.398732133764691</v>
+        <v>0.4041066691564266</v>
       </c>
       <c r="D5" t="n">
-        <v>2.572498618429586</v>
+        <v>2.56125358609114</v>
       </c>
       <c r="E5" t="n">
-        <v>1.753634376995053</v>
+        <v>1.722720249009499</v>
       </c>
       <c r="F5" t="n">
-        <v>11.40348575662846</v>
+        <v>11.07068904226662</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.3892029208226518</v>
+        <v>0.4012945541335625</v>
       </c>
       <c r="D6" t="n">
-        <v>2.597452979392447</v>
+        <v>2.56466168751983</v>
       </c>
       <c r="E6" t="n">
-        <v>1.693708568646101</v>
+        <v>1.604388690086644</v>
       </c>
       <c r="F6" t="n">
-        <v>11.00674175245207</v>
+        <v>10.21126081730861</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -1164,16 +1164,16 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3702880735716577</v>
+        <v>0.4015377454027587</v>
       </c>
       <c r="E2" t="n">
-        <v>2.305024456381418</v>
+        <v>2.247102901284053</v>
       </c>
       <c r="F2" t="n">
-        <v>1.539169348223839</v>
+        <v>1.47646540084388</v>
       </c>
       <c r="G2" t="n">
-        <v>10.34390825287467</v>
+        <v>9.922465910465334</v>
       </c>
     </row>
     <row r="3">
@@ -1191,16 +1191,16 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4775121928822613</v>
+        <v>0.526154792462501</v>
       </c>
       <c r="E3" t="n">
-        <v>2.518257008536305</v>
+        <v>2.398171389668895</v>
       </c>
       <c r="F3" t="n">
-        <v>1.632227553575185</v>
+        <v>1.530081645569619</v>
       </c>
       <c r="G3" t="n">
-        <v>10.07094822888103</v>
+        <v>9.410586514416019</v>
       </c>
     </row>
     <row r="4">
@@ -1218,16 +1218,16 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5643773005380752</v>
+        <v>0.5904034131806324</v>
       </c>
       <c r="E4" t="n">
-        <v>2.001612728930465</v>
+        <v>1.940899140532581</v>
       </c>
       <c r="F4" t="n">
-        <v>1.429332677404348</v>
+        <v>1.39386434599156</v>
       </c>
       <c r="G4" t="n">
-        <v>9.538782294363644</v>
+        <v>9.249174606340071</v>
       </c>
     </row>
     <row r="5">
@@ -1245,16 +1245,16 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4436394517952583</v>
+        <v>0.4492266175267953</v>
       </c>
       <c r="E5" t="n">
-        <v>2.515926976409569</v>
+        <v>2.50326219417127</v>
       </c>
       <c r="F5" t="n">
-        <v>1.526555461791202</v>
+        <v>1.502428874734609</v>
       </c>
       <c r="G5" t="n">
-        <v>9.559118485251197</v>
+        <v>9.309695478537984</v>
       </c>
     </row>
     <row r="6">
@@ -1272,16 +1272,16 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3582904679118309</v>
+        <v>0.3792788035941768</v>
       </c>
       <c r="E6" t="n">
-        <v>3.121142102178442</v>
+        <v>3.069676325804024</v>
       </c>
       <c r="F6" t="n">
-        <v>1.858690210056495</v>
+        <v>1.799888535031846</v>
       </c>
       <c r="G6" t="n">
-        <v>11.1139983185385</v>
+        <v>10.74873259634901</v>
       </c>
     </row>
     <row r="7">
@@ -1299,16 +1299,16 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4307982338134093</v>
+        <v>0.4921050851862889</v>
       </c>
       <c r="E7" t="n">
-        <v>2.191480939823528</v>
+        <v>2.070100882792117</v>
       </c>
       <c r="F7" t="n">
-        <v>1.463787737341771</v>
+        <v>1.348342616033752</v>
       </c>
       <c r="G7" t="n">
-        <v>9.597159016181552</v>
+        <v>8.850431925043631</v>
       </c>
     </row>
     <row r="8">
@@ -1326,16 +1326,16 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5445341047434713</v>
+        <v>0.6022918301486293</v>
       </c>
       <c r="E8" t="n">
-        <v>2.351201785046227</v>
+        <v>2.197071686983065</v>
       </c>
       <c r="F8" t="n">
-        <v>1.509909614225436</v>
+        <v>1.422623839662446</v>
       </c>
       <c r="G8" t="n">
-        <v>9.841628232468222</v>
+        <v>9.136907946025028</v>
       </c>
     </row>
     <row r="9">
@@ -1353,16 +1353,16 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5405513660113825</v>
+        <v>0.5324335348160025</v>
       </c>
       <c r="E9" t="n">
-        <v>2.055622135032329</v>
+        <v>2.073702641042575</v>
       </c>
       <c r="F9" t="n">
-        <v>1.427372808251288</v>
+        <v>1.430940295358649</v>
       </c>
       <c r="G9" t="n">
-        <v>9.077482397235464</v>
+        <v>8.993695474295889</v>
       </c>
     </row>
     <row r="10">
@@ -1380,16 +1380,16 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4428260349503099</v>
+        <v>0.4860936110184395</v>
       </c>
       <c r="E10" t="n">
-        <v>2.51776548735817</v>
+        <v>2.418031070610126</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5003340552017</v>
+        <v>1.425195541401274</v>
       </c>
       <c r="G10" t="n">
-        <v>8.797954199321607</v>
+        <v>8.298017367358993</v>
       </c>
     </row>
     <row r="11">
@@ -1407,16 +1407,16 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4363952885513575</v>
+        <v>0.4599978235333507</v>
       </c>
       <c r="E11" t="n">
-        <v>2.925038618392301</v>
+        <v>2.863136489897156</v>
       </c>
       <c r="F11" t="n">
-        <v>1.749549299363057</v>
+        <v>1.719862208067939</v>
       </c>
       <c r="G11" t="n">
-        <v>10.85335127474795</v>
+        <v>10.50172313355208</v>
       </c>
     </row>
     <row r="12">
@@ -1434,16 +1434,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3325701574480541</v>
+        <v>0.3391971885866912</v>
       </c>
       <c r="E12" t="n">
-        <v>2.373052732147749</v>
+        <v>2.361242107523141</v>
       </c>
       <c r="F12" t="n">
-        <v>1.703520238897469</v>
+        <v>1.519681488743311</v>
       </c>
       <c r="G12" t="n">
-        <v>11.81203055985724</v>
+        <v>10.2263668811902</v>
       </c>
     </row>
     <row r="13">
@@ -1461,16 +1461,16 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5196382969760538</v>
+        <v>0.5613640609441286</v>
       </c>
       <c r="E13" t="n">
-        <v>2.414605353444562</v>
+        <v>2.307353187896521</v>
       </c>
       <c r="F13" t="n">
-        <v>1.601538847353268</v>
+        <v>1.529611498274475</v>
       </c>
       <c r="G13" t="n">
-        <v>10.53391292861681</v>
+        <v>10.01857004224986</v>
       </c>
     </row>
     <row r="14">
@@ -1488,16 +1488,16 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3049577158718695</v>
+        <v>0.2796470998064836</v>
       </c>
       <c r="E14" t="n">
-        <v>2.528310547593204</v>
+        <v>2.57393430260522</v>
       </c>
       <c r="F14" t="n">
-        <v>1.646172383314446</v>
+        <v>1.620011617322511</v>
       </c>
       <c r="G14" t="n">
-        <v>10.26310526409532</v>
+        <v>9.92482676321551</v>
       </c>
     </row>
     <row r="15">
@@ -1515,16 +1515,16 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4906886019535568</v>
+        <v>0.4629454224329047</v>
       </c>
       <c r="E15" t="n">
-        <v>2.407196627738349</v>
+        <v>2.471889654535175</v>
       </c>
       <c r="F15" t="n">
-        <v>1.535758577334653</v>
+        <v>1.5485793393129</v>
       </c>
       <c r="G15" t="n">
-        <v>9.826428706301396</v>
+        <v>9.435626916834176</v>
       </c>
     </row>
     <row r="16">
@@ -1542,16 +1542,16 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2981598318637253</v>
+        <v>0.3633189988976043</v>
       </c>
       <c r="E16" t="n">
-        <v>3.264099636038372</v>
+        <v>3.108889185039096</v>
       </c>
       <c r="F16" t="n">
-        <v>1.98155279633067</v>
+        <v>1.804059506780023</v>
       </c>
       <c r="G16" t="n">
-        <v>12.59823130338961</v>
+        <v>11.45091348305329</v>
       </c>
     </row>
     <row r="17">
@@ -1569,16 +1569,16 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3081414786113043</v>
+        <v>0.3363215730070706</v>
       </c>
       <c r="E17" t="n">
-        <v>2.416090654380424</v>
+        <v>2.366374238823536</v>
       </c>
       <c r="F17" t="n">
-        <v>1.696929526684865</v>
+        <v>1.591060840532472</v>
       </c>
       <c r="G17" t="n">
-        <v>11.52572390200825</v>
+        <v>10.57986722665282</v>
       </c>
     </row>
     <row r="18">
@@ -1596,16 +1596,16 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4215032241787866</v>
+        <v>0.4638000330871673</v>
       </c>
       <c r="E18" t="n">
-        <v>2.649796015146564</v>
+        <v>2.55108754638635</v>
       </c>
       <c r="F18" t="n">
-        <v>1.806030218274586</v>
+        <v>1.776180592898495</v>
       </c>
       <c r="G18" t="n">
-        <v>12.01320004918785</v>
+        <v>11.66768665646218</v>
       </c>
     </row>
     <row r="19">
@@ -1623,16 +1623,16 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3230005748246274</v>
+        <v>0.3203747054320681</v>
       </c>
       <c r="E19" t="n">
-        <v>2.495278089620727</v>
+        <v>2.500112608568134</v>
       </c>
       <c r="F19" t="n">
-        <v>1.824995743571001</v>
+        <v>1.78514571015618</v>
       </c>
       <c r="G19" t="n">
-        <v>11.97058085844532</v>
+        <v>11.74069759972516</v>
       </c>
     </row>
     <row r="20">
@@ -1650,16 +1650,16 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5180587272081942</v>
+        <v>0.4439062366013358</v>
       </c>
       <c r="E20" t="n">
-        <v>2.341622749386803</v>
+        <v>2.515323688149471</v>
       </c>
       <c r="F20" t="n">
-        <v>1.551956288002059</v>
+        <v>1.612440432698072</v>
       </c>
       <c r="G20" t="n">
-        <v>9.763139485247104</v>
+        <v>9.884461686310214</v>
       </c>
     </row>
     <row r="21">
@@ -1677,16 +1677,16 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4229566640005425</v>
+        <v>0.4561307976544915</v>
       </c>
       <c r="E21" t="n">
-        <v>2.959705583613412</v>
+        <v>2.873369848528209</v>
       </c>
       <c r="F21" t="n">
-        <v>1.888260108442756</v>
+        <v>1.848773668762279</v>
       </c>
       <c r="G21" t="n">
-        <v>11.7447844882538</v>
+        <v>11.48073204218273</v>
       </c>
     </row>
     <row r="22">
@@ -1704,16 +1704,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3867277772682304</v>
+        <v>0.3372961985579841</v>
       </c>
       <c r="E22" t="n">
-        <v>2.274737176713528</v>
+        <v>2.364636065600208</v>
       </c>
       <c r="F22" t="n">
-        <v>1.601427891765505</v>
+        <v>1.610978207194598</v>
       </c>
       <c r="G22" t="n">
-        <v>10.90088843762073</v>
+        <v>10.82854740139946</v>
       </c>
     </row>
     <row r="23">
@@ -1731,16 +1731,16 @@
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5059497043389669</v>
+        <v>0.5493056142525183</v>
       </c>
       <c r="E23" t="n">
-        <v>2.448767501883184</v>
+        <v>2.338853638891928</v>
       </c>
       <c r="F23" t="n">
-        <v>1.648459500166954</v>
+        <v>1.625921075521627</v>
       </c>
       <c r="G23" t="n">
-        <v>10.86184108108688</v>
+        <v>10.6114096453814</v>
       </c>
     </row>
     <row r="24">
@@ -1758,16 +1758,16 @@
         <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4662751269819717</v>
+        <v>0.4486943163963046</v>
       </c>
       <c r="E24" t="n">
-        <v>2.215560044727363</v>
+        <v>2.251754493728487</v>
       </c>
       <c r="F24" t="n">
-        <v>1.522872488193711</v>
+        <v>1.54304571975113</v>
       </c>
       <c r="G24" t="n">
-        <v>9.959266879544298</v>
+        <v>10.19277402867325</v>
       </c>
     </row>
     <row r="25">
@@ -1785,16 +1785,16 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4637989869586896</v>
+        <v>0.4712146815302456</v>
       </c>
       <c r="E25" t="n">
-        <v>2.469924531787909</v>
+        <v>2.452785459113523</v>
       </c>
       <c r="F25" t="n">
-        <v>1.523085402045285</v>
+        <v>1.526819039469361</v>
       </c>
       <c r="G25" t="n">
-        <v>9.59427611816731</v>
+        <v>9.489429275775372</v>
       </c>
     </row>
     <row r="26">
@@ -1812,16 +1812,16 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4243456949844134</v>
+        <v>0.4578531165281005</v>
       </c>
       <c r="E26" t="n">
-        <v>2.956141206807906</v>
+        <v>2.868816563185415</v>
       </c>
       <c r="F26" t="n">
-        <v>1.839867979928314</v>
+        <v>1.774570098910459</v>
       </c>
       <c r="G26" t="n">
-        <v>11.34475257099355</v>
+        <v>10.89009889050769</v>
       </c>
     </row>
   </sheetData>
@@ -1888,7 +1888,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-15 07:33:39 UTC</t>
+          <t>2026-06-16 14:10:37 UTC</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/NN/reports/model_comparison.xlsx
+++ b/NN/reports/model_comparison.xlsx
@@ -553,28 +553,28 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.5145843769405423</v>
+        <v>0.4685535509360278</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2.324408554265008</v>
+        <v>2.428363111432299</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1.469392900104812</v>
+        <v>1.540242880439229</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9.156155169255126</v>
+        <v>9.737159352503387</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.05547054150310088</v>
+        <v>0.05329406220579078</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.3326911062311046</v>
+        <v>0.2900066311631516</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.144055024077614</v>
+        <v>0.1128821833322044</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.8165757686407459</v>
+        <v>0.787156633239385</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>5</v>
@@ -598,28 +598,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4693202744333728</v>
+        <v>0.4265547479132713</v>
       </c>
       <c r="F3" t="n">
-        <v>2.431822390292165</v>
+        <v>2.525850362055937</v>
       </c>
       <c r="G3" t="n">
-        <v>1.540545760434303</v>
+        <v>1.613442122804021</v>
       </c>
       <c r="H3" t="n">
-        <v>9.728131021221682</v>
+        <v>10.19373827933255</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08802979849040111</v>
+        <v>0.07637605842602378</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4147953125467814</v>
+        <v>0.3716218126818406</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1536577359258706</v>
+        <v>0.1542138721205013</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6294274558814178</v>
+        <v>0.6968161636237368</v>
       </c>
       <c r="M3" t="n">
         <v>5</v>
@@ -643,28 +643,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.4528727854530306</v>
+        <v>0.3704770852294791</v>
       </c>
       <c r="F4" t="n">
-        <v>2.455369244103912</v>
+        <v>2.625130578071788</v>
       </c>
       <c r="G4" t="n">
-        <v>1.616266828169435</v>
+        <v>1.669514958864082</v>
       </c>
       <c r="H4" t="n">
-        <v>10.40245184834743</v>
+        <v>10.61758285457678</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07588795418503885</v>
+        <v>0.1155351232379027</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2419776457187243</v>
+        <v>0.2586165974478284</v>
       </c>
       <c r="K4" t="n">
-        <v>0.09816228546697167</v>
+        <v>0.152208993513278</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5789204230913501</v>
+        <v>0.9702394358124595</v>
       </c>
       <c r="M4" t="n">
         <v>5</v>
@@ -688,28 +688,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.4041066691564266</v>
+        <v>0.3209906084893889</v>
       </c>
       <c r="F5" t="n">
-        <v>2.56125358609114</v>
+        <v>2.729056441080148</v>
       </c>
       <c r="G5" t="n">
-        <v>1.722720249009499</v>
+        <v>1.841476824995353</v>
       </c>
       <c r="H5" t="n">
-        <v>11.07068904226662</v>
+        <v>11.95654027242562</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06974896813083979</v>
+        <v>0.1228642299585319</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1879798155985191</v>
+        <v>0.2809817960582253</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1141711970306861</v>
+        <v>0.1397116667702418</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8095514614440562</v>
+        <v>0.9102716370175346</v>
       </c>
       <c r="M5" t="n">
         <v>5</v>
@@ -733,28 +733,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.4012945541335625</v>
+        <v>0.3161223771862539</v>
       </c>
       <c r="F6" t="n">
-        <v>2.56466168751983</v>
+        <v>2.738540149523886</v>
       </c>
       <c r="G6" t="n">
-        <v>1.604388690086644</v>
+        <v>1.733873939403339</v>
       </c>
       <c r="H6" t="n">
-        <v>10.21126081730861</v>
+        <v>11.07441665210726</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1112647802768699</v>
+        <v>0.1299546977472318</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3211165637487183</v>
+        <v>0.3346652025815746</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1183153972470814</v>
+        <v>0.1834117476726411</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7512904023338809</v>
+        <v>1.282366852322866</v>
       </c>
       <c r="M6" t="n">
         <v>5</v>
@@ -780,13 +780,13 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.5145843769405423</v>
+        <v>0.4685535509360278</v>
       </c>
       <c r="F2" t="n">
-        <v>2.324408554265008</v>
+        <v>2.428363111432299</v>
       </c>
       <c r="G2" t="n">
-        <v>1.469392900104812</v>
+        <v>1.540242880439229</v>
       </c>
       <c r="H2" t="n">
-        <v>9.156155169255126</v>
+        <v>9.737159352503387</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05547054150310088</v>
+        <v>0.05329406220579078</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3326911062311046</v>
+        <v>0.2900066311631516</v>
       </c>
       <c r="K2" t="n">
-        <v>0.144055024077614</v>
+        <v>0.1128821833322044</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8165757686407459</v>
+        <v>0.787156633239385</v>
       </c>
       <c r="M2" t="n">
         <v>5</v>
@@ -973,16 +973,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5145843769405423</v>
+        <v>0.4685535509360278</v>
       </c>
       <c r="D2" t="n">
-        <v>2.324408554265008</v>
+        <v>2.428363111432299</v>
       </c>
       <c r="E2" t="n">
-        <v>1.469392900104812</v>
+        <v>1.540242880439229</v>
       </c>
       <c r="F2" t="n">
-        <v>9.156155169255126</v>
+        <v>9.737159352503387</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -998,16 +998,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.4693202744333728</v>
+        <v>0.4265547479132713</v>
       </c>
       <c r="D3" t="n">
-        <v>2.431822390292165</v>
+        <v>2.525850362055937</v>
       </c>
       <c r="E3" t="n">
-        <v>1.540545760434303</v>
+        <v>1.613442122804021</v>
       </c>
       <c r="F3" t="n">
-        <v>9.728131021221682</v>
+        <v>10.19373827933255</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -1023,16 +1023,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.4528727854530306</v>
+        <v>0.3704770852294791</v>
       </c>
       <c r="D4" t="n">
-        <v>2.455369244103912</v>
+        <v>2.625130578071788</v>
       </c>
       <c r="E4" t="n">
-        <v>1.616266828169435</v>
+        <v>1.669514958864082</v>
       </c>
       <c r="F4" t="n">
-        <v>10.40245184834743</v>
+        <v>10.61758285457678</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -1048,16 +1048,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.4041066691564266</v>
+        <v>0.3209906084893889</v>
       </c>
       <c r="D5" t="n">
-        <v>2.56125358609114</v>
+        <v>2.729056441080148</v>
       </c>
       <c r="E5" t="n">
-        <v>1.722720249009499</v>
+        <v>1.841476824995353</v>
       </c>
       <c r="F5" t="n">
-        <v>11.07068904226662</v>
+        <v>11.95654027242562</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.4012945541335625</v>
+        <v>0.3161223771862539</v>
       </c>
       <c r="D6" t="n">
-        <v>2.56466168751983</v>
+        <v>2.738540149523886</v>
       </c>
       <c r="E6" t="n">
-        <v>1.604388690086644</v>
+        <v>1.733873939403339</v>
       </c>
       <c r="F6" t="n">
-        <v>10.21126081730861</v>
+        <v>11.07441665210726</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -1164,16 +1164,16 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4015377454027587</v>
+        <v>0.3405411464552272</v>
       </c>
       <c r="E2" t="n">
-        <v>2.247102901284053</v>
+        <v>2.358839707715803</v>
       </c>
       <c r="F2" t="n">
-        <v>1.47646540084388</v>
+        <v>1.548544488016418</v>
       </c>
       <c r="G2" t="n">
-        <v>9.922465910465334</v>
+        <v>10.42289098949631</v>
       </c>
     </row>
     <row r="3">
@@ -1191,16 +1191,16 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0.526154792462501</v>
+        <v>0.4886357664786484</v>
       </c>
       <c r="E3" t="n">
-        <v>2.398171389668895</v>
+        <v>2.491306411160191</v>
       </c>
       <c r="F3" t="n">
-        <v>1.530081645569619</v>
+        <v>1.620151678673872</v>
       </c>
       <c r="G3" t="n">
-        <v>9.410586514416019</v>
+        <v>10.06486942753843</v>
       </c>
     </row>
     <row r="4">
@@ -1218,16 +1218,16 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5904034131806324</v>
+        <v>0.5105116999435453</v>
       </c>
       <c r="E4" t="n">
-        <v>1.940899140532581</v>
+        <v>2.121758550462867</v>
       </c>
       <c r="F4" t="n">
-        <v>1.39386434599156</v>
+        <v>1.522321299911785</v>
       </c>
       <c r="G4" t="n">
-        <v>9.249174606340071</v>
+        <v>9.959408766567247</v>
       </c>
     </row>
     <row r="5">
@@ -1245,16 +1245,16 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4492266175267953</v>
+        <v>0.436733261655682</v>
       </c>
       <c r="E5" t="n">
-        <v>2.50326219417127</v>
+        <v>2.531494112792314</v>
       </c>
       <c r="F5" t="n">
-        <v>1.502428874734609</v>
+        <v>1.499123858969313</v>
       </c>
       <c r="G5" t="n">
-        <v>9.309695478537984</v>
+        <v>9.309656885446525</v>
       </c>
     </row>
     <row r="6">
@@ -1272,16 +1272,16 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3792788035941768</v>
+        <v>0.3563518650332537</v>
       </c>
       <c r="E6" t="n">
-        <v>3.069676325804024</v>
+        <v>3.125853028148511</v>
       </c>
       <c r="F6" t="n">
-        <v>1.799888535031846</v>
+        <v>1.87706928844872</v>
       </c>
       <c r="G6" t="n">
-        <v>10.74873259634901</v>
+        <v>11.21186532761424</v>
       </c>
     </row>
     <row r="7">
@@ -1299,16 +1299,16 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4921050851862889</v>
+        <v>0.3957121463201557</v>
       </c>
       <c r="E7" t="n">
-        <v>2.070100882792117</v>
+        <v>2.258013378454343</v>
       </c>
       <c r="F7" t="n">
-        <v>1.348342616033752</v>
+        <v>1.481328816083395</v>
       </c>
       <c r="G7" t="n">
-        <v>8.850431925043631</v>
+        <v>9.734582447729334</v>
       </c>
     </row>
     <row r="8">
@@ -1326,16 +1326,16 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6022918301486293</v>
+        <v>0.5372451113249948</v>
       </c>
       <c r="E8" t="n">
-        <v>2.197071686983065</v>
+        <v>2.369940697966636</v>
       </c>
       <c r="F8" t="n">
-        <v>1.422623839662446</v>
+        <v>1.533216679076694</v>
       </c>
       <c r="G8" t="n">
-        <v>9.136907946025028</v>
+        <v>10.01805989333302</v>
       </c>
     </row>
     <row r="9">
@@ -1353,16 +1353,16 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5324335348160025</v>
+        <v>0.4892400018125445</v>
       </c>
       <c r="E9" t="n">
-        <v>2.073702641042575</v>
+        <v>2.167370917669783</v>
       </c>
       <c r="F9" t="n">
-        <v>1.430940295358649</v>
+        <v>1.507132388989348</v>
       </c>
       <c r="G9" t="n">
-        <v>8.993695474295889</v>
+        <v>9.541258026088169</v>
       </c>
     </row>
     <row r="10">
@@ -1380,16 +1380,16 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4860936110184395</v>
+        <v>0.4799317312773388</v>
       </c>
       <c r="E10" t="n">
-        <v>2.418031070610126</v>
+        <v>2.43248430579403</v>
       </c>
       <c r="F10" t="n">
-        <v>1.425195541401274</v>
+        <v>1.445810828025478</v>
       </c>
       <c r="G10" t="n">
-        <v>8.298017367358993</v>
+        <v>8.610182003127491</v>
       </c>
     </row>
     <row r="11">
@@ -1407,16 +1407,16 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4599978235333507</v>
+        <v>0.4406387639451054</v>
       </c>
       <c r="E11" t="n">
-        <v>2.863136489897156</v>
+        <v>2.914006257276704</v>
       </c>
       <c r="F11" t="n">
-        <v>1.719862208067939</v>
+        <v>1.733725690021231</v>
       </c>
       <c r="G11" t="n">
-        <v>10.50172313355208</v>
+        <v>10.78171439223892</v>
       </c>
     </row>
     <row r="12">
@@ -1434,16 +1434,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3391971885866912</v>
+        <v>0.2195508574994395</v>
       </c>
       <c r="E12" t="n">
-        <v>2.361242107523141</v>
+        <v>2.566119531159044</v>
       </c>
       <c r="F12" t="n">
-        <v>1.519681488743311</v>
+        <v>1.651170364052434</v>
       </c>
       <c r="G12" t="n">
-        <v>10.2263668811902</v>
+        <v>11.23574150316772</v>
       </c>
     </row>
     <row r="13">
@@ -1461,16 +1461,16 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5613640609441286</v>
+        <v>0.5217796836511164</v>
       </c>
       <c r="E13" t="n">
-        <v>2.307353187896521</v>
+        <v>2.409217352030585</v>
       </c>
       <c r="F13" t="n">
-        <v>1.529611498274475</v>
+        <v>1.591347164526004</v>
       </c>
       <c r="G13" t="n">
-        <v>10.01857004224986</v>
+        <v>10.47680425005608</v>
       </c>
     </row>
     <row r="14">
@@ -1488,16 +1488,16 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2796470998064836</v>
+        <v>0.1997908351831014</v>
       </c>
       <c r="E14" t="n">
-        <v>2.57393430260522</v>
+        <v>2.712854888010491</v>
       </c>
       <c r="F14" t="n">
-        <v>1.620011617322511</v>
+        <v>1.740636475176751</v>
       </c>
       <c r="G14" t="n">
-        <v>9.92482676321551</v>
+        <v>10.79766232916917</v>
       </c>
     </row>
     <row r="15">
@@ -1515,16 +1515,16 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4629454224329047</v>
+        <v>0.3541881756975337</v>
       </c>
       <c r="E15" t="n">
-        <v>2.471889654535175</v>
+        <v>2.710646378605534</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5485793393129</v>
+        <v>1.638784709250092</v>
       </c>
       <c r="G15" t="n">
-        <v>9.435626916834176</v>
+        <v>9.71864594147803</v>
       </c>
     </row>
     <row r="16">
@@ -1542,16 +1542,16 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3633189988976043</v>
+        <v>0.2853023339000788</v>
       </c>
       <c r="E16" t="n">
-        <v>3.108889185039096</v>
+        <v>3.293862597813778</v>
       </c>
       <c r="F16" t="n">
-        <v>1.804059506780023</v>
+        <v>2.047430984011412</v>
       </c>
       <c r="G16" t="n">
-        <v>11.45091348305329</v>
+        <v>13.14322923666531</v>
       </c>
     </row>
     <row r="17">
@@ -1569,16 +1569,16 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3363215730070706</v>
+        <v>0.2495236511184644</v>
       </c>
       <c r="E17" t="n">
-        <v>2.366374238823536</v>
+        <v>2.51636179785694</v>
       </c>
       <c r="F17" t="n">
-        <v>1.591060840532472</v>
+        <v>1.745541835978233</v>
       </c>
       <c r="G17" t="n">
-        <v>10.57986722665282</v>
+        <v>11.94219727043234</v>
       </c>
     </row>
     <row r="18">
@@ -1596,16 +1596,16 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4638000330871673</v>
+        <v>0.4161951094082808</v>
       </c>
       <c r="E18" t="n">
-        <v>2.55108754638635</v>
+        <v>2.661925126408518</v>
       </c>
       <c r="F18" t="n">
-        <v>1.776180592898495</v>
+        <v>1.869785799419726</v>
       </c>
       <c r="G18" t="n">
-        <v>11.66768665646218</v>
+        <v>12.52520119230864</v>
       </c>
     </row>
     <row r="19">
@@ -1623,16 +1623,16 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3203747054320681</v>
+        <v>0.152562324394501</v>
       </c>
       <c r="E19" t="n">
-        <v>2.500112608568134</v>
+        <v>2.791763900765353</v>
       </c>
       <c r="F19" t="n">
-        <v>1.78514571015618</v>
+        <v>1.939562315783906</v>
       </c>
       <c r="G19" t="n">
-        <v>11.74069759972516</v>
+        <v>12.48984816847153</v>
       </c>
     </row>
     <row r="20">
@@ -1650,16 +1650,16 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4439062366013358</v>
+        <v>0.4540618420295943</v>
       </c>
       <c r="E20" t="n">
-        <v>2.515323688149471</v>
+        <v>2.492249936550893</v>
       </c>
       <c r="F20" t="n">
-        <v>1.612440432698072</v>
+        <v>1.65597109647615</v>
       </c>
       <c r="G20" t="n">
-        <v>9.884461686310214</v>
+        <v>10.3843999415379</v>
       </c>
     </row>
     <row r="21">
@@ -1677,16 +1677,16 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4561307976544915</v>
+        <v>0.332610115496104</v>
       </c>
       <c r="E21" t="n">
-        <v>2.873369848528209</v>
+        <v>3.182981443819036</v>
       </c>
       <c r="F21" t="n">
-        <v>1.848773668762279</v>
+        <v>1.996523077318749</v>
       </c>
       <c r="G21" t="n">
-        <v>11.48073204218273</v>
+        <v>12.44105478937768</v>
       </c>
     </row>
     <row r="22">
@@ -1704,16 +1704,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3372961985579841</v>
+        <v>0.2658935920388783</v>
       </c>
       <c r="E22" t="n">
-        <v>2.364636065600208</v>
+        <v>2.488766118675989</v>
       </c>
       <c r="F22" t="n">
-        <v>1.610978207194598</v>
+        <v>1.626601767771183</v>
       </c>
       <c r="G22" t="n">
-        <v>10.82854740139946</v>
+        <v>10.85251639901629</v>
       </c>
     </row>
     <row r="23">
@@ -1731,16 +1731,16 @@
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5493056142525183</v>
+        <v>0.5302207362385831</v>
       </c>
       <c r="E23" t="n">
-        <v>2.338853638891928</v>
+        <v>2.387860176799714</v>
       </c>
       <c r="F23" t="n">
-        <v>1.625921075521627</v>
+        <v>1.640365280098226</v>
       </c>
       <c r="G23" t="n">
-        <v>10.6114096453814</v>
+        <v>10.84921930842765</v>
       </c>
     </row>
     <row r="24">
@@ -1758,16 +1758,16 @@
         <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4486943163963046</v>
+        <v>0.2514688367442799</v>
       </c>
       <c r="E24" t="n">
-        <v>2.251754493728487</v>
+        <v>2.623794069720723</v>
       </c>
       <c r="F24" t="n">
-        <v>1.54304571975113</v>
+        <v>1.647467128646059</v>
       </c>
       <c r="G24" t="n">
-        <v>10.19277402867325</v>
+        <v>10.31613979150895</v>
       </c>
     </row>
     <row r="25">
@@ -1785,16 +1785,16 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4712146815302456</v>
+        <v>0.4215905178943229</v>
       </c>
       <c r="E25" t="n">
-        <v>2.452785459113523</v>
+        <v>2.565296511298319</v>
       </c>
       <c r="F25" t="n">
-        <v>1.526819039469361</v>
+        <v>1.510336768551271</v>
       </c>
       <c r="G25" t="n">
-        <v>9.489429275775372</v>
+        <v>9.202332690564692</v>
       </c>
     </row>
     <row r="26">
@@ -1812,16 +1812,16 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4578531165281005</v>
+        <v>0.3832117432313314</v>
       </c>
       <c r="E26" t="n">
-        <v>2.868816563185415</v>
+        <v>3.059936013864194</v>
       </c>
       <c r="F26" t="n">
-        <v>1.774570098910459</v>
+        <v>1.922803849253669</v>
       </c>
       <c r="G26" t="n">
-        <v>10.89009889050769</v>
+        <v>11.86770608336634</v>
       </c>
     </row>
   </sheetData>
@@ -1888,7 +1888,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16 14:10:37 UTC</t>
+          <t>2026-06-16 15:30:39 UTC</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/NN/reports/model_comparison.xlsx
+++ b/NN/reports/model_comparison.xlsx
@@ -457,7 +457,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -565,16 +565,16 @@
         <v>9.737159352503387</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.05329406220579078</v>
+        <v>0.05329406220579082</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>0.2900066311631516</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.1128821833322044</v>
+        <v>0.1128821833322042</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.787156633239385</v>
+        <v>0.7871566332393861</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>5</v>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4265547479132713</v>
+        <v>0.4265547479132714</v>
       </c>
       <c r="F3" t="n">
         <v>2.525850362055937</v>
@@ -610,16 +610,16 @@
         <v>10.19373827933255</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07637605842602378</v>
+        <v>0.07637605842602388</v>
       </c>
       <c r="J3" t="n">
         <v>0.3716218126818406</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1542138721205013</v>
+        <v>0.1542138721205016</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6968161636237368</v>
+        <v>0.6968161636237377</v>
       </c>
       <c r="M3" t="n">
         <v>5</v>
@@ -784,9 +784,9 @@
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
@@ -887,16 +887,16 @@
         <v>9.737159352503387</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05329406220579078</v>
+        <v>0.05329406220579082</v>
       </c>
       <c r="J2" t="n">
         <v>0.2900066311631516</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1128821833322044</v>
+        <v>0.1128821833322042</v>
       </c>
       <c r="L2" t="n">
-        <v>0.787156633239385</v>
+        <v>0.7871566332393861</v>
       </c>
       <c r="M2" t="n">
         <v>5</v>
@@ -919,7 +919,7 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.4265547479132713</v>
+        <v>0.4265547479132714</v>
       </c>
       <c r="D3" t="n">
         <v>2.525850362055937</v>
@@ -1164,13 +1164,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3405411464552272</v>
+        <v>0.340541146455227</v>
       </c>
       <c r="E2" t="n">
         <v>2.358839707715803</v>
       </c>
       <c r="F2" t="n">
-        <v>1.548544488016418</v>
+        <v>1.548544488016417</v>
       </c>
       <c r="G2" t="n">
         <v>10.42289098949631</v>
@@ -1218,7 +1218,7 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5105116999435453</v>
+        <v>0.5105116999435455</v>
       </c>
       <c r="E4" t="n">
         <v>2.121758550462867</v>
@@ -1227,7 +1227,7 @@
         <v>1.522321299911785</v>
       </c>
       <c r="G4" t="n">
-        <v>9.959408766567247</v>
+        <v>9.959408766567245</v>
       </c>
     </row>
     <row r="5">
@@ -1245,7 +1245,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.436733261655682</v>
+        <v>0.4367332616556822</v>
       </c>
       <c r="E5" t="n">
         <v>2.531494112792314</v>
@@ -1254,7 +1254,7 @@
         <v>1.499123858969313</v>
       </c>
       <c r="G5" t="n">
-        <v>9.309656885446525</v>
+        <v>9.309656885446524</v>
       </c>
     </row>
     <row r="6">
@@ -1281,7 +1281,7 @@
         <v>1.87706928844872</v>
       </c>
       <c r="G6" t="n">
-        <v>11.21186532761424</v>
+        <v>11.21186532761425</v>
       </c>
     </row>
     <row r="7">
@@ -1299,7 +1299,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3957121463201557</v>
+        <v>0.3957121463201556</v>
       </c>
       <c r="E7" t="n">
         <v>2.258013378454343</v>
@@ -1308,7 +1308,7 @@
         <v>1.481328816083395</v>
       </c>
       <c r="G7" t="n">
-        <v>9.734582447729334</v>
+        <v>9.734582447729338</v>
       </c>
     </row>
     <row r="8">
@@ -1362,7 +1362,7 @@
         <v>1.507132388989348</v>
       </c>
       <c r="G9" t="n">
-        <v>9.541258026088169</v>
+        <v>9.541258026088165</v>
       </c>
     </row>
     <row r="10">
@@ -1389,7 +1389,7 @@
         <v>1.445810828025478</v>
       </c>
       <c r="G10" t="n">
-        <v>8.610182003127491</v>
+        <v>8.610182003127489</v>
       </c>
     </row>
     <row r="11">
@@ -1888,7 +1888,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16 15:30:39 UTC</t>
+          <t>2026-06-16 15:41:54 UTC</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/NN/reports/model_comparison.xlsx
+++ b/NN/reports/model_comparison.xlsx
@@ -553,28 +553,28 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.4685535509360278</v>
+        <v>0.3475619114126487</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2.428363111432299</v>
+        <v>2.670064625179535</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1.540242880439229</v>
+        <v>1.724001666595458</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9.737159352503387</v>
+        <v>10.73288760387268</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.05329406220579082</v>
+        <v>0.1345139021054229</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.2900066311631516</v>
+        <v>0.2759938661529209</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.1128821833322042</v>
+        <v>0.1300793588913376</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.7871566332393861</v>
+        <v>0.6088549516517517</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>5</v>
@@ -598,28 +598,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4265547479132714</v>
+        <v>0.2772283325377834</v>
       </c>
       <c r="F3" t="n">
-        <v>2.525850362055937</v>
+        <v>2.818132432409113</v>
       </c>
       <c r="G3" t="n">
-        <v>1.613442122804021</v>
+        <v>1.810619855358758</v>
       </c>
       <c r="H3" t="n">
-        <v>10.19373827933255</v>
+        <v>11.15675759386654</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07637605842602388</v>
+        <v>0.1271045053242389</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3716218126818406</v>
+        <v>0.2973293184753861</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1542138721205016</v>
+        <v>0.162476129112051</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6968161636237377</v>
+        <v>0.7153119678951047</v>
       </c>
       <c r="M3" t="n">
         <v>5</v>
@@ -643,28 +643,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.3704770852294791</v>
+        <v>0.2502294268481291</v>
       </c>
       <c r="F4" t="n">
-        <v>2.625130578071788</v>
+        <v>2.868457507988512</v>
       </c>
       <c r="G4" t="n">
-        <v>1.669514958864082</v>
+        <v>1.828589195077021</v>
       </c>
       <c r="H4" t="n">
-        <v>10.61758285457678</v>
+        <v>11.29583617410455</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1155351232379027</v>
+        <v>0.1246204234685471</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2586165974478284</v>
+        <v>0.2616543215769145</v>
       </c>
       <c r="K4" t="n">
-        <v>0.152208993513278</v>
+        <v>0.1313446833503343</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9702394358124595</v>
+        <v>0.7952564532360673</v>
       </c>
       <c r="M4" t="n">
         <v>5</v>
@@ -688,28 +688,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.3209906084893889</v>
+        <v>0.2426041813485177</v>
       </c>
       <c r="F5" t="n">
-        <v>2.729056441080148</v>
+        <v>2.878408257206955</v>
       </c>
       <c r="G5" t="n">
-        <v>1.841476824995353</v>
+        <v>2.01898665643334</v>
       </c>
       <c r="H5" t="n">
-        <v>11.95654027242562</v>
+        <v>13.08944628033598</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1228642299585319</v>
+        <v>0.1487389697577027</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2809817960582253</v>
+        <v>0.2703204693829702</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1397116667702418</v>
+        <v>0.1308037603691884</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9102716370175346</v>
+        <v>0.5533642650241283</v>
       </c>
       <c r="M5" t="n">
         <v>5</v>
@@ -733,28 +733,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.3161223771862539</v>
+        <v>0.2168752240204649</v>
       </c>
       <c r="F6" t="n">
-        <v>2.738540149523886</v>
+        <v>2.934672119506324</v>
       </c>
       <c r="G6" t="n">
-        <v>1.733873939403339</v>
+        <v>1.912556921237381</v>
       </c>
       <c r="H6" t="n">
-        <v>11.07441665210726</v>
+        <v>12.04146650634223</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1299546977472318</v>
+        <v>0.1379902834731904</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3346652025815746</v>
+        <v>0.3301731664486217</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1834117476726411</v>
+        <v>0.1445206900573864</v>
       </c>
       <c r="L6" t="n">
-        <v>1.282366852322866</v>
+        <v>0.7819771492459937</v>
       </c>
       <c r="M6" t="n">
         <v>5</v>
@@ -780,12 +780,12 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.4685535509360278</v>
+        <v>0.3475619114126487</v>
       </c>
       <c r="F2" t="n">
-        <v>2.428363111432299</v>
+        <v>2.670064625179535</v>
       </c>
       <c r="G2" t="n">
-        <v>1.540242880439229</v>
+        <v>1.724001666595458</v>
       </c>
       <c r="H2" t="n">
-        <v>9.737159352503387</v>
+        <v>10.73288760387268</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05329406220579082</v>
+        <v>0.1345139021054229</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2900066311631516</v>
+        <v>0.2759938661529209</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1128821833322042</v>
+        <v>0.1300793588913376</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7871566332393861</v>
+        <v>0.6088549516517517</v>
       </c>
       <c r="M2" t="n">
         <v>5</v>
@@ -973,16 +973,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4685535509360278</v>
+        <v>0.3475619114126487</v>
       </c>
       <c r="D2" t="n">
-        <v>2.428363111432299</v>
+        <v>2.670064625179535</v>
       </c>
       <c r="E2" t="n">
-        <v>1.540242880439229</v>
+        <v>1.724001666595458</v>
       </c>
       <c r="F2" t="n">
-        <v>9.737159352503387</v>
+        <v>10.73288760387268</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -998,16 +998,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.4265547479132714</v>
+        <v>0.2772283325377834</v>
       </c>
       <c r="D3" t="n">
-        <v>2.525850362055937</v>
+        <v>2.818132432409113</v>
       </c>
       <c r="E3" t="n">
-        <v>1.613442122804021</v>
+        <v>1.810619855358758</v>
       </c>
       <c r="F3" t="n">
-        <v>10.19373827933255</v>
+        <v>11.15675759386654</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -1023,16 +1023,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.3704770852294791</v>
+        <v>0.2502294268481291</v>
       </c>
       <c r="D4" t="n">
-        <v>2.625130578071788</v>
+        <v>2.868457507988512</v>
       </c>
       <c r="E4" t="n">
-        <v>1.669514958864082</v>
+        <v>1.828589195077021</v>
       </c>
       <c r="F4" t="n">
-        <v>10.61758285457678</v>
+        <v>11.29583617410455</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -1048,16 +1048,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.3209906084893889</v>
+        <v>0.2426041813485177</v>
       </c>
       <c r="D5" t="n">
-        <v>2.729056441080148</v>
+        <v>2.878408257206955</v>
       </c>
       <c r="E5" t="n">
-        <v>1.841476824995353</v>
+        <v>2.01898665643334</v>
       </c>
       <c r="F5" t="n">
-        <v>11.95654027242562</v>
+        <v>13.08944628033598</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.3161223771862539</v>
+        <v>0.2168752240204649</v>
       </c>
       <c r="D6" t="n">
-        <v>2.738540149523886</v>
+        <v>2.934672119506324</v>
       </c>
       <c r="E6" t="n">
-        <v>1.733873939403339</v>
+        <v>1.912556921237381</v>
       </c>
       <c r="F6" t="n">
-        <v>11.07441665210726</v>
+        <v>12.04146650634223</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -1106,7 +1106,7 @@
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
@@ -1164,16 +1164,16 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.340541146455227</v>
+        <v>0.1375242572258365</v>
       </c>
       <c r="E2" t="n">
-        <v>2.358839707715803</v>
+        <v>2.69760291939645</v>
       </c>
       <c r="F2" t="n">
-        <v>1.548544488016417</v>
+        <v>1.791107558260881</v>
       </c>
       <c r="G2" t="n">
-        <v>10.42289098949631</v>
+        <v>11.60488795979047</v>
       </c>
     </row>
     <row r="3">
@@ -1191,16 +1191,16 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4886357664786484</v>
+        <v>0.3934126684102763</v>
       </c>
       <c r="E3" t="n">
-        <v>2.491306411160191</v>
+        <v>2.713367627392175</v>
       </c>
       <c r="F3" t="n">
-        <v>1.620151678673872</v>
+        <v>1.742412199603735</v>
       </c>
       <c r="G3" t="n">
-        <v>10.06486942753843</v>
+        <v>11.0464471361651</v>
       </c>
     </row>
     <row r="4">
@@ -1218,16 +1218,16 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5105116999435455</v>
+        <v>0.3538266322060785</v>
       </c>
       <c r="E4" t="n">
-        <v>2.121758550462867</v>
+        <v>2.437807060094935</v>
       </c>
       <c r="F4" t="n">
-        <v>1.522321299911785</v>
+        <v>1.615808515150031</v>
       </c>
       <c r="G4" t="n">
-        <v>9.959408766567245</v>
+        <v>10.20494034307571</v>
       </c>
     </row>
     <row r="5">
@@ -1245,16 +1245,16 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4367332616556822</v>
+        <v>0.14039348078986</v>
       </c>
       <c r="E5" t="n">
-        <v>2.531494112792314</v>
+        <v>3.127301252768773</v>
       </c>
       <c r="F5" t="n">
-        <v>1.499123858969313</v>
+        <v>1.845354914662583</v>
       </c>
       <c r="G5" t="n">
-        <v>9.309656885446524</v>
+        <v>10.85579114424698</v>
       </c>
     </row>
     <row r="6">
@@ -1272,16 +1272,16 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3563518650332537</v>
+        <v>0.3609846240568655</v>
       </c>
       <c r="E6" t="n">
-        <v>3.125853028148511</v>
+        <v>3.114583302393233</v>
       </c>
       <c r="F6" t="n">
-        <v>1.87706928844872</v>
+        <v>2.058416089116561</v>
       </c>
       <c r="G6" t="n">
-        <v>11.21186532761425</v>
+        <v>12.07172138605443</v>
       </c>
     </row>
     <row r="7">
@@ -1299,16 +1299,16 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3957121463201556</v>
+        <v>0.2168452105174348</v>
       </c>
       <c r="E7" t="n">
-        <v>2.258013378454343</v>
+        <v>2.570563771095248</v>
       </c>
       <c r="F7" t="n">
-        <v>1.481328816083395</v>
+        <v>1.68065622362869</v>
       </c>
       <c r="G7" t="n">
-        <v>9.734582447729338</v>
+        <v>10.61719655576705</v>
       </c>
     </row>
     <row r="8">
@@ -1326,16 +1326,16 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5372451113249948</v>
+        <v>0.4967186540018255</v>
       </c>
       <c r="E8" t="n">
-        <v>2.369940697966636</v>
+        <v>2.471538545991182</v>
       </c>
       <c r="F8" t="n">
-        <v>1.533216679076694</v>
+        <v>1.645617791842475</v>
       </c>
       <c r="G8" t="n">
-        <v>10.01805989333302</v>
+        <v>10.7902196972945</v>
       </c>
     </row>
     <row r="9">
@@ -1353,16 +1353,16 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4892400018125445</v>
+        <v>0.380121254206484</v>
       </c>
       <c r="E9" t="n">
-        <v>2.167370917669783</v>
+        <v>2.387691294816318</v>
       </c>
       <c r="F9" t="n">
-        <v>1.507132388989348</v>
+        <v>1.587539217065166</v>
       </c>
       <c r="G9" t="n">
-        <v>9.541258026088165</v>
+        <v>10.03734168475668</v>
       </c>
     </row>
     <row r="10">
@@ -1380,16 +1380,16 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4799317312773388</v>
+        <v>0.1982058703740011</v>
       </c>
       <c r="E10" t="n">
-        <v>2.43248430579403</v>
+        <v>3.020308498636547</v>
       </c>
       <c r="F10" t="n">
-        <v>1.445810828025478</v>
+        <v>1.791024187489793</v>
       </c>
       <c r="G10" t="n">
-        <v>8.610182003127489</v>
+        <v>10.51900350835138</v>
       </c>
     </row>
     <row r="11">
@@ -1407,16 +1407,16 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4406387639451054</v>
+        <v>0.445918567963498</v>
       </c>
       <c r="E11" t="n">
-        <v>2.914006257276704</v>
+        <v>2.90022101535838</v>
       </c>
       <c r="F11" t="n">
-        <v>1.733725690021231</v>
+        <v>1.915170912951167</v>
       </c>
       <c r="G11" t="n">
-        <v>10.78171439223892</v>
+        <v>11.7006765731938</v>
       </c>
     </row>
     <row r="12">
@@ -1434,16 +1434,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2195508574994395</v>
+        <v>0.05968772445445791</v>
       </c>
       <c r="E12" t="n">
-        <v>2.566119531159044</v>
+        <v>2.816700242406141</v>
       </c>
       <c r="F12" t="n">
-        <v>1.651170364052434</v>
+        <v>1.913470109384271</v>
       </c>
       <c r="G12" t="n">
-        <v>11.23574150316772</v>
+        <v>12.40565826936212</v>
       </c>
     </row>
     <row r="13">
@@ -1461,16 +1461,16 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5217796836511164</v>
+        <v>0.3710543602833046</v>
       </c>
       <c r="E13" t="n">
-        <v>2.409217352030585</v>
+        <v>2.762921376778704</v>
       </c>
       <c r="F13" t="n">
-        <v>1.591347164526004</v>
+        <v>1.87258234109577</v>
       </c>
       <c r="G13" t="n">
-        <v>10.47680425005608</v>
+        <v>12.42328500697347</v>
       </c>
     </row>
     <row r="14">
@@ -1488,16 +1488,16 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1997908351831014</v>
+        <v>0.2979343900969972</v>
       </c>
       <c r="E14" t="n">
-        <v>2.712854888010491</v>
+        <v>2.541052589161022</v>
       </c>
       <c r="F14" t="n">
-        <v>1.740636475176751</v>
+        <v>1.693547171007229</v>
       </c>
       <c r="G14" t="n">
-        <v>10.79766232916917</v>
+        <v>10.71755881321576</v>
       </c>
     </row>
     <row r="15">
@@ -1515,16 +1515,16 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3541881756975337</v>
+        <v>0.08279824468351682</v>
       </c>
       <c r="E15" t="n">
-        <v>2.710646378605534</v>
+        <v>3.230370288517931</v>
       </c>
       <c r="F15" t="n">
-        <v>1.638784709250092</v>
+        <v>2.023146753979336</v>
       </c>
       <c r="G15" t="n">
-        <v>9.71864594147803</v>
+        <v>11.97840830305187</v>
       </c>
     </row>
     <row r="16">
@@ -1542,16 +1542,16 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2853023339000788</v>
+        <v>0.2729014005840478</v>
       </c>
       <c r="E16" t="n">
-        <v>3.293862597813778</v>
+        <v>3.322316100667821</v>
       </c>
       <c r="F16" t="n">
-        <v>2.047430984011412</v>
+        <v>2.060038230720297</v>
       </c>
       <c r="G16" t="n">
-        <v>13.14322923666531</v>
+        <v>12.68242213910793</v>
       </c>
     </row>
     <row r="17">
@@ -1569,16 +1569,16 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2495236511184644</v>
+        <v>0.03363184196721503</v>
       </c>
       <c r="E17" t="n">
-        <v>2.51636179785694</v>
+        <v>2.85545870582219</v>
       </c>
       <c r="F17" t="n">
-        <v>1.745541835978233</v>
+        <v>2.017145159274588</v>
       </c>
       <c r="G17" t="n">
-        <v>11.94219727043234</v>
+        <v>13.45356244323637</v>
       </c>
     </row>
     <row r="18">
@@ -1596,16 +1596,16 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4161951094082808</v>
+        <v>0.372106954635132</v>
       </c>
       <c r="E18" t="n">
-        <v>2.661925126408518</v>
+        <v>2.760608415954663</v>
       </c>
       <c r="F18" t="n">
-        <v>1.869785799419726</v>
+        <v>1.991764742259174</v>
       </c>
       <c r="G18" t="n">
-        <v>12.52520119230864</v>
+        <v>13.23549517874973</v>
       </c>
     </row>
     <row r="19">
@@ -1623,16 +1623,16 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>0.152562324394501</v>
+        <v>0.3203624060435829</v>
       </c>
       <c r="E19" t="n">
-        <v>2.791763900765353</v>
+        <v>2.500135231120115</v>
       </c>
       <c r="F19" t="n">
-        <v>1.939562315783906</v>
+        <v>1.82832930530693</v>
       </c>
       <c r="G19" t="n">
-        <v>12.48984816847153</v>
+        <v>12.22296775681971</v>
       </c>
     </row>
     <row r="20">
@@ -1650,16 +1650,16 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4540618420295943</v>
+        <v>0.138567260006538</v>
       </c>
       <c r="E20" t="n">
-        <v>2.492249936550893</v>
+        <v>3.130621441904872</v>
       </c>
       <c r="F20" t="n">
-        <v>1.65597109647615</v>
+        <v>2.068825212809891</v>
       </c>
       <c r="G20" t="n">
-        <v>10.3843999415379</v>
+        <v>12.90936251608409</v>
       </c>
     </row>
     <row r="21">
@@ -1677,16 +1677,16 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.332610115496104</v>
+        <v>0.3483524440901209</v>
       </c>
       <c r="E21" t="n">
-        <v>3.182981443819036</v>
+        <v>3.145217491232934</v>
       </c>
       <c r="F21" t="n">
-        <v>1.996523077318749</v>
+        <v>2.188868862516117</v>
       </c>
       <c r="G21" t="n">
-        <v>12.44105478937768</v>
+        <v>13.62584350678997</v>
       </c>
     </row>
     <row r="22">
@@ -1704,16 +1704,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2658935920388783</v>
+        <v>0.1155835041933543</v>
       </c>
       <c r="E22" t="n">
-        <v>2.488766118675989</v>
+        <v>2.731699954451646</v>
       </c>
       <c r="F22" t="n">
-        <v>1.626601767771183</v>
+        <v>1.855511970800285</v>
       </c>
       <c r="G22" t="n">
-        <v>10.85251639901629</v>
+        <v>12.10616692642842</v>
       </c>
     </row>
     <row r="23">
@@ -1731,16 +1731,16 @@
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5302207362385831</v>
+        <v>0.3753288385945706</v>
       </c>
       <c r="E23" t="n">
-        <v>2.387860176799714</v>
+        <v>2.753516603717938</v>
       </c>
       <c r="F23" t="n">
-        <v>1.640365280098226</v>
+        <v>1.820372903661957</v>
       </c>
       <c r="G23" t="n">
-        <v>10.84921930842765</v>
+        <v>11.77343971567986</v>
       </c>
     </row>
     <row r="24">
@@ -1758,16 +1758,16 @@
         <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2514688367442799</v>
+        <v>0.2823572884744895</v>
       </c>
       <c r="E24" t="n">
-        <v>2.623794069720723</v>
+        <v>2.569087774418126</v>
       </c>
       <c r="F24" t="n">
-        <v>1.647467128646059</v>
+        <v>1.636502460601098</v>
       </c>
       <c r="G24" t="n">
-        <v>10.31613979150895</v>
+        <v>10.43389469559245</v>
       </c>
     </row>
     <row r="25">
@@ -1785,16 +1785,16 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4215905178943229</v>
+        <v>0.1226321431595566</v>
       </c>
       <c r="E25" t="n">
-        <v>2.565296511298319</v>
+        <v>3.159444482427975</v>
       </c>
       <c r="F25" t="n">
-        <v>1.510336768551271</v>
+        <v>1.825041603698744</v>
       </c>
       <c r="G25" t="n">
-        <v>9.202332690564692</v>
+        <v>10.44592839784901</v>
       </c>
     </row>
     <row r="26">
@@ -1812,16 +1812,16 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3832117432313314</v>
+        <v>0.3552453598186746</v>
       </c>
       <c r="E26" t="n">
-        <v>3.059936013864194</v>
+        <v>3.128538724926872</v>
       </c>
       <c r="F26" t="n">
-        <v>1.922803849253669</v>
+        <v>2.005517036623017</v>
       </c>
       <c r="G26" t="n">
-        <v>11.86770608336634</v>
+        <v>11.71975113497303</v>
       </c>
     </row>
   </sheetData>
@@ -1888,7 +1888,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16 15:41:54 UTC</t>
+          <t>2026-06-16 16:28:03 UTC</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/NN/reports/model_comparison.xlsx
+++ b/NN/reports/model_comparison.xlsx
@@ -453,17 +453,17 @@
   <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
@@ -538,7 +538,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,28 +553,28 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.3475619114126487</v>
+        <v>0.7075824164304918</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2.670064625179535</v>
+        <v>0.2265145849180154</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1.724001666595458</v>
+        <v>0.1534632768361582</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10.73288760387268</v>
+        <v>11.28813559322034</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.1345139021054229</v>
+        <v>0.05769637344403198</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.2759938661529209</v>
+        <v>0.02264141774146809</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.1300793588913376</v>
+        <v>0.01761644976276228</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.6088549516517517</v>
+        <v>1.091018728676065</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>5</v>
@@ -583,7 +583,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -594,32 +594,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.2772283325377834</v>
+        <v>0.6891342697800888</v>
       </c>
       <c r="F3" t="n">
-        <v>2.818132432409113</v>
+        <v>0.2334507636116066</v>
       </c>
       <c r="G3" t="n">
-        <v>1.810619855358758</v>
+        <v>0.159833193145213</v>
       </c>
       <c r="H3" t="n">
-        <v>11.15675759386654</v>
+        <v>11.31896148721601</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1271045053242389</v>
+        <v>0.05455241665986311</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2973293184753861</v>
+        <v>0.0166691295033356</v>
       </c>
       <c r="K3" t="n">
-        <v>0.162476129112051</v>
+        <v>0.01510922812252184</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7153119678951047</v>
+        <v>0.8825239049015797</v>
       </c>
       <c r="M3" t="n">
         <v>5</v>
@@ -628,7 +628,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -643,28 +643,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.2502294268481291</v>
+        <v>0.631129215306083</v>
       </c>
       <c r="F4" t="n">
-        <v>2.868457507988512</v>
+        <v>0.2542475858244539</v>
       </c>
       <c r="G4" t="n">
-        <v>1.828589195077021</v>
+        <v>0.1745126960764377</v>
       </c>
       <c r="H4" t="n">
-        <v>11.29583617410455</v>
+        <v>12.65527712440974</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1246204234685471</v>
+        <v>0.06622259284727117</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2616543215769145</v>
+        <v>0.01806679891144974</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1313446833503343</v>
+        <v>0.01820807899175943</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7952564532360673</v>
+        <v>1.067676143917996</v>
       </c>
       <c r="M4" t="n">
         <v>5</v>
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -684,32 +684,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.2426041813485177</v>
+        <v>0.6004528082484381</v>
       </c>
       <c r="F5" t="n">
-        <v>2.878408257206955</v>
+        <v>0.2642198828533087</v>
       </c>
       <c r="G5" t="n">
-        <v>2.01898665643334</v>
+        <v>0.1424584300841315</v>
       </c>
       <c r="H5" t="n">
-        <v>13.08944628033598</v>
+        <v>10.3845632884462</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1487389697577027</v>
+        <v>0.0773795390752951</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2703204693829702</v>
+        <v>0.01721382159644064</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1308037603691884</v>
+        <v>0.01711653095647098</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5533642650241283</v>
+        <v>0.9753908287223869</v>
       </c>
       <c r="M5" t="n">
         <v>5</v>
@@ -718,7 +718,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -729,32 +729,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.2168752240204649</v>
+        <v>0.599146075639495</v>
       </c>
       <c r="F6" t="n">
-        <v>2.934672119506324</v>
+        <v>0.2643673972632752</v>
       </c>
       <c r="G6" t="n">
-        <v>1.912556921237381</v>
+        <v>0.171090395480226</v>
       </c>
       <c r="H6" t="n">
-        <v>12.04146650634223</v>
+        <v>12.73135593220339</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1379902834731904</v>
+        <v>0.09519719042744534</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3301731664486217</v>
+        <v>0.0292826945301505</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1445206900573864</v>
+        <v>0.0225782356361301</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7819771492459937</v>
+        <v>1.34277002378688</v>
       </c>
       <c r="M6" t="n">
         <v>5</v>
@@ -775,17 +775,17 @@
   <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
@@ -860,7 +860,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.3475619114126487</v>
+        <v>0.7075824164304918</v>
       </c>
       <c r="F2" t="n">
-        <v>2.670064625179535</v>
+        <v>0.2265145849180154</v>
       </c>
       <c r="G2" t="n">
-        <v>1.724001666595458</v>
+        <v>0.1534632768361582</v>
       </c>
       <c r="H2" t="n">
-        <v>10.73288760387268</v>
+        <v>11.28813559322034</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1345139021054229</v>
+        <v>0.05769637344403198</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2759938661529209</v>
+        <v>0.02264141774146809</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1300793588913376</v>
+        <v>0.01761644976276228</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6088549516517517</v>
+        <v>1.091018728676065</v>
       </c>
       <c r="M2" t="n">
         <v>5</v>
@@ -919,9 +919,9 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
@@ -973,16 +973,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3475619114126487</v>
+        <v>0.7075824164304918</v>
       </c>
       <c r="D2" t="n">
-        <v>2.670064625179535</v>
+        <v>0.2265145849180154</v>
       </c>
       <c r="E2" t="n">
-        <v>1.724001666595458</v>
+        <v>0.1534632768361582</v>
       </c>
       <c r="F2" t="n">
-        <v>10.73288760387268</v>
+        <v>11.28813559322034</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -994,20 +994,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2772283325377834</v>
+        <v>0.6891342697800888</v>
       </c>
       <c r="D3" t="n">
-        <v>2.818132432409113</v>
+        <v>0.2334507636116066</v>
       </c>
       <c r="E3" t="n">
-        <v>1.810619855358758</v>
+        <v>0.159833193145213</v>
       </c>
       <c r="F3" t="n">
-        <v>11.15675759386654</v>
+        <v>11.31896148721601</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -1023,16 +1023,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.2502294268481291</v>
+        <v>0.631129215306083</v>
       </c>
       <c r="D4" t="n">
-        <v>2.868457507988512</v>
+        <v>0.2542475858244539</v>
       </c>
       <c r="E4" t="n">
-        <v>1.828589195077021</v>
+        <v>0.1745126960764377</v>
       </c>
       <c r="F4" t="n">
-        <v>11.29583617410455</v>
+        <v>12.65527712440974</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -1044,20 +1044,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.2426041813485177</v>
+        <v>0.6004528082484381</v>
       </c>
       <c r="D5" t="n">
-        <v>2.878408257206955</v>
+        <v>0.2642198828533087</v>
       </c>
       <c r="E5" t="n">
-        <v>2.01898665643334</v>
+        <v>0.1424584300841315</v>
       </c>
       <c r="F5" t="n">
-        <v>13.08944628033598</v>
+        <v>10.3845632884462</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.2168752240204649</v>
+        <v>0.599146075639495</v>
       </c>
       <c r="D6" t="n">
-        <v>2.934672119506324</v>
+        <v>0.2643673972632752</v>
       </c>
       <c r="E6" t="n">
-        <v>1.912556921237381</v>
+        <v>0.171090395480226</v>
       </c>
       <c r="F6" t="n">
-        <v>12.04146650634223</v>
+        <v>12.73135593220339</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -1103,12 +1103,12 @@
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -1152,7 +1152,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1164,22 +1164,22 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1375242572258365</v>
+        <v>0.5096979117415289</v>
       </c>
       <c r="E2" t="n">
-        <v>2.69760291939645</v>
+        <v>0.2818508908455553</v>
       </c>
       <c r="F2" t="n">
-        <v>1.791107558260881</v>
+        <v>0.1988135593220339</v>
       </c>
       <c r="G2" t="n">
-        <v>11.60488795979047</v>
+        <v>13.82344632768362</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1191,22 +1191,22 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3934126684102763</v>
+        <v>0.514668423091825</v>
       </c>
       <c r="E3" t="n">
-        <v>2.713367627392175</v>
+        <v>0.2999378466689503</v>
       </c>
       <c r="F3" t="n">
-        <v>1.742412199603735</v>
+        <v>0.1805649717514124</v>
       </c>
       <c r="G3" t="n">
-        <v>11.0464471361651</v>
+        <v>13.8093220338983</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1218,22 +1218,22 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3538266322060785</v>
+        <v>0.5752523049645392</v>
       </c>
       <c r="E4" t="n">
-        <v>2.437807060094935</v>
+        <v>0.2623330784857232</v>
       </c>
       <c r="F4" t="n">
-        <v>1.615808515150031</v>
+        <v>0.1653672316384181</v>
       </c>
       <c r="G4" t="n">
-        <v>10.20494034307571</v>
+        <v>12.50988700564972</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1245,22 +1245,22 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.14039348078986</v>
+        <v>0.6759723271935036</v>
       </c>
       <c r="E5" t="n">
-        <v>3.127301252768773</v>
+        <v>0.2554909236210373</v>
       </c>
       <c r="F5" t="n">
-        <v>1.845354914662583</v>
+        <v>0.1734180790960452</v>
       </c>
       <c r="G5" t="n">
-        <v>10.85579114424698</v>
+        <v>12.96327683615819</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1272,22 +1272,22 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3609846240568655</v>
+        <v>0.7201394112060779</v>
       </c>
       <c r="E6" t="n">
-        <v>3.114583302393233</v>
+        <v>0.2222242466951098</v>
       </c>
       <c r="F6" t="n">
-        <v>2.058416089116561</v>
+        <v>0.1372881355932203</v>
       </c>
       <c r="G6" t="n">
-        <v>12.07172138605443</v>
+        <v>10.55084745762712</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1299,22 +1299,22 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2168452105174348</v>
+        <v>0.6641486603624902</v>
       </c>
       <c r="E7" t="n">
-        <v>2.570563771095248</v>
+        <v>0.2332711781622523</v>
       </c>
       <c r="F7" t="n">
-        <v>1.68065622362869</v>
+        <v>0.1704519774011299</v>
       </c>
       <c r="G7" t="n">
-        <v>10.61719655576705</v>
+        <v>11.64406779661017</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1326,22 +1326,22 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4967186540018255</v>
+        <v>0.6355832450815792</v>
       </c>
       <c r="E8" t="n">
-        <v>2.471538545991182</v>
+        <v>0.2599029226272901</v>
       </c>
       <c r="F8" t="n">
-        <v>1.645617791842475</v>
+        <v>0.1657062146892656</v>
       </c>
       <c r="G8" t="n">
-        <v>10.7902196972945</v>
+        <v>12.35875706214689</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1353,22 +1353,22 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0.380121254206484</v>
+        <v>0.7153261623325453</v>
       </c>
       <c r="E9" t="n">
-        <v>2.387691294816318</v>
+        <v>0.2147639180347625</v>
       </c>
       <c r="F9" t="n">
-        <v>1.587539217065166</v>
+        <v>0.1442372881355932</v>
       </c>
       <c r="G9" t="n">
-        <v>10.03734168475668</v>
+        <v>10.63983050847457</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1380,22 +1380,22 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1982058703740011</v>
+        <v>0.7475225351554763</v>
       </c>
       <c r="E10" t="n">
-        <v>3.020308498636547</v>
+        <v>0.225525542333504</v>
       </c>
       <c r="F10" t="n">
-        <v>1.791024187489793</v>
+        <v>0.1595480225988701</v>
       </c>
       <c r="G10" t="n">
-        <v>10.51900350835138</v>
+        <v>12.07485875706215</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1407,22 +1407,22 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.445918567963498</v>
+        <v>0.7753314792203682</v>
       </c>
       <c r="E11" t="n">
-        <v>2.90022101535838</v>
+        <v>0.1991093634322681</v>
       </c>
       <c r="F11" t="n">
-        <v>1.915170912951167</v>
+        <v>0.1273728813559322</v>
       </c>
       <c r="G11" t="n">
-        <v>11.7006765731938</v>
+        <v>9.72316384180791</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1434,22 +1434,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.05968772445445791</v>
+        <v>0.5210533609048746</v>
       </c>
       <c r="E12" t="n">
-        <v>2.816700242406141</v>
+        <v>0.2785679225259067</v>
       </c>
       <c r="F12" t="n">
-        <v>1.913470109384271</v>
+        <v>0.1710112115084115</v>
       </c>
       <c r="G12" t="n">
-        <v>12.40565826936212</v>
+        <v>11.13615627005949</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1461,22 +1461,22 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3710543602833046</v>
+        <v>0.5908801533502738</v>
       </c>
       <c r="E13" t="n">
-        <v>2.762921376778704</v>
+        <v>0.2753830901183061</v>
       </c>
       <c r="F13" t="n">
-        <v>1.87258234109577</v>
+        <v>0.1350980941521919</v>
       </c>
       <c r="G13" t="n">
-        <v>12.42328500697347</v>
+        <v>10.95348581419153</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1488,22 +1488,22 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2979343900969972</v>
+        <v>0.5309857944042633</v>
       </c>
       <c r="E14" t="n">
-        <v>2.541052589161022</v>
+        <v>0.2756643079434532</v>
       </c>
       <c r="F14" t="n">
-        <v>1.693547171007229</v>
+        <v>0.143752475411205</v>
       </c>
       <c r="G14" t="n">
-        <v>10.71755881321576</v>
+        <v>11.16535512067504</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1515,22 +1515,22 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0.08279824468351682</v>
+        <v>0.689088351218363</v>
       </c>
       <c r="E15" t="n">
-        <v>3.230370288517931</v>
+        <v>0.2502666166407419</v>
       </c>
       <c r="F15" t="n">
-        <v>2.023146753979336</v>
+        <v>0.1361126823950622</v>
       </c>
       <c r="G15" t="n">
-        <v>11.97840830305187</v>
+        <v>9.110748161703853</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1542,22 +1542,22 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2729014005840478</v>
+        <v>0.6702563813644158</v>
       </c>
       <c r="E16" t="n">
-        <v>3.322316100667821</v>
+        <v>0.2412174770381354</v>
       </c>
       <c r="F16" t="n">
-        <v>2.060038230720297</v>
+        <v>0.1263176869537871</v>
       </c>
       <c r="G16" t="n">
-        <v>12.68242213910793</v>
+        <v>9.557071075601092</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1569,22 +1569,22 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.03363184196721503</v>
+        <v>0.6304427922362768</v>
       </c>
       <c r="E17" t="n">
-        <v>2.85545870582219</v>
+        <v>0.2446968501165838</v>
       </c>
       <c r="F17" t="n">
-        <v>2.017145159274588</v>
+        <v>0.1775684001307204</v>
       </c>
       <c r="G17" t="n">
-        <v>13.45356244323637</v>
+        <v>11.69486161741834</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1596,22 +1596,22 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>0.372106954635132</v>
+        <v>0.6476515300032419</v>
       </c>
       <c r="E18" t="n">
-        <v>2.760608415954663</v>
+        <v>0.2555631249789595</v>
       </c>
       <c r="F18" t="n">
-        <v>1.991764742259174</v>
+        <v>0.1676182587655647</v>
       </c>
       <c r="G18" t="n">
-        <v>13.23549517874973</v>
+        <v>12.3492082015384</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1623,22 +1623,22 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3203624060435829</v>
+        <v>0.6753266710911043</v>
       </c>
       <c r="E19" t="n">
-        <v>2.500135231120115</v>
+        <v>0.2293563915689381</v>
       </c>
       <c r="F19" t="n">
-        <v>1.82832930530693</v>
+        <v>0.1527719954896816</v>
       </c>
       <c r="G19" t="n">
-        <v>12.22296775681971</v>
+        <v>10.85019748437418</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1650,22 +1650,22 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>0.138567260006538</v>
+        <v>0.7512134213950209</v>
       </c>
       <c r="E20" t="n">
-        <v>3.130621441904872</v>
+        <v>0.2238710309712114</v>
       </c>
       <c r="F20" t="n">
-        <v>2.068825212809891</v>
+        <v>0.1632088341289259</v>
       </c>
       <c r="G20" t="n">
-        <v>12.90936251608409</v>
+        <v>11.64197758317975</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1677,22 +1677,22 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3483524440901209</v>
+        <v>0.7410369341748004</v>
       </c>
       <c r="E21" t="n">
-        <v>3.145217491232934</v>
+        <v>0.2137664204223401</v>
       </c>
       <c r="F21" t="n">
-        <v>2.188868862516117</v>
+        <v>0.1379984772111725</v>
       </c>
       <c r="G21" t="n">
-        <v>13.62584350678997</v>
+        <v>10.05856254956937</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1704,22 +1704,22 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1155835041933543</v>
+        <v>0.5540882866801717</v>
       </c>
       <c r="E22" t="n">
-        <v>2.731699954451646</v>
+        <v>0.2687893027252355</v>
       </c>
       <c r="F22" t="n">
-        <v>1.855511970800285</v>
+        <v>0.1989311682213938</v>
       </c>
       <c r="G22" t="n">
-        <v>12.10616692642842</v>
+        <v>13.63927893854905</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1731,22 +1731,22 @@
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3753288385945706</v>
+        <v>0.6303479541754455</v>
       </c>
       <c r="E23" t="n">
-        <v>2.753516603717938</v>
+        <v>0.2617631764008746</v>
       </c>
       <c r="F23" t="n">
-        <v>1.820372903661957</v>
+        <v>0.1749535940170056</v>
       </c>
       <c r="G23" t="n">
-        <v>11.77343971567986</v>
+        <v>12.93940970810529</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1758,22 +1758,22 @@
         <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2823572884744895</v>
+        <v>0.5821788447193872</v>
       </c>
       <c r="E24" t="n">
-        <v>2.569087774418126</v>
+        <v>0.2601852982435431</v>
       </c>
       <c r="F24" t="n">
-        <v>1.636502460601098</v>
+        <v>0.1750747792351021</v>
       </c>
       <c r="G24" t="n">
-        <v>10.43389469559245</v>
+        <v>12.95547232460194</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1785,22 +1785,22 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1226321431595566</v>
+        <v>0.6702870787671645</v>
       </c>
       <c r="E25" t="n">
-        <v>3.159444482427975</v>
+        <v>0.2577225436645673</v>
       </c>
       <c r="F25" t="n">
-        <v>1.825041603698744</v>
+        <v>0.1760539747411815</v>
       </c>
       <c r="G25" t="n">
-        <v>10.44592839784901</v>
+        <v>12.91772411483323</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1812,16 +1812,16 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3552453598186746</v>
+        <v>0.7187439121882457</v>
       </c>
       <c r="E26" t="n">
-        <v>3.128538724926872</v>
+        <v>0.2227776080880491</v>
       </c>
       <c r="F26" t="n">
-        <v>2.005517036623017</v>
+        <v>0.1475499641675053</v>
       </c>
       <c r="G26" t="n">
-        <v>11.71975113497303</v>
+        <v>10.82450053595918</v>
       </c>
     </row>
   </sheetData>
@@ -1888,7 +1888,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16 16:28:03 UTC</t>
+          <t>2026-06-16 17:02:47 UTC</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/NN/reports/model_comparison.xlsx
+++ b/NN/reports/model_comparison.xlsx
@@ -453,17 +453,17 @@
   <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
@@ -538,7 +538,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,28 +553,28 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.7075824164304918</v>
+        <v>0.4086956512454042</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.2265145849180154</v>
+        <v>2.535338649478117</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.1534632768361582</v>
+        <v>1.586123962213442</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>11.28813559322034</v>
+        <v>9.653121526592447</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.05769637344403198</v>
+        <v>0.1243675999133593</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.02264141774146809</v>
+        <v>0.2094044716037683</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.01761644976276228</v>
+        <v>0.1161712416186803</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1.091018728676065</v>
+        <v>0.8405404365051592</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>5</v>
@@ -583,7 +583,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -598,28 +598,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.6891342697800888</v>
+        <v>0.3460798162399042</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2334507636116066</v>
+        <v>2.667324015363976</v>
       </c>
       <c r="G3" t="n">
-        <v>0.159833193145213</v>
+        <v>1.772661726891013</v>
       </c>
       <c r="H3" t="n">
-        <v>11.31896148721601</v>
+        <v>11.33148578435193</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05455241665986311</v>
+        <v>0.1182842703918661</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0166691295033356</v>
+        <v>0.1059367242493817</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01510922812252184</v>
+        <v>0.06870580702931066</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8825239049015797</v>
+        <v>0.5387119334359428</v>
       </c>
       <c r="M3" t="n">
         <v>5</v>
@@ -628,7 +628,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -643,28 +643,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.631129215306083</v>
+        <v>0.309031006433505</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2542475858244539</v>
+        <v>2.740271040236071</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1745126960764377</v>
+        <v>1.733584190785634</v>
       </c>
       <c r="H4" t="n">
-        <v>12.65527712440974</v>
+        <v>10.7822156512856</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06622259284727117</v>
+        <v>0.1335865599922902</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01806679891144974</v>
+        <v>0.1743519699278086</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01820807899175943</v>
+        <v>0.0440645637655039</v>
       </c>
       <c r="L4" t="n">
-        <v>1.067676143917996</v>
+        <v>0.6255646156502747</v>
       </c>
       <c r="M4" t="n">
         <v>5</v>
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -684,32 +684,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.6004528082484381</v>
+        <v>0.3067468478319929</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2642198828533087</v>
+        <v>2.745453465559433</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1424584300841315</v>
+        <v>1.705698004783789</v>
       </c>
       <c r="H5" t="n">
-        <v>10.3845632884462</v>
+        <v>10.33745886530554</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0773795390752951</v>
+        <v>0.1364673246088052</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01721382159644064</v>
+        <v>0.1638065689272675</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01711653095647098</v>
+        <v>0.08907696999215506</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9753908287223869</v>
+        <v>0.7148236202024966</v>
       </c>
       <c r="M5" t="n">
         <v>5</v>
@@ -718,7 +718,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -729,32 +729,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.599146075639495</v>
+        <v>0.2539176593976449</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2643673972632752</v>
+        <v>2.834278764941554</v>
       </c>
       <c r="G6" t="n">
-        <v>0.171090395480226</v>
+        <v>1.748594033518405</v>
       </c>
       <c r="H6" t="n">
-        <v>12.73135593220339</v>
+        <v>10.95046767711853</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09519719042744534</v>
+        <v>0.2003719663564008</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0292826945301505</v>
+        <v>0.2544127199870098</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0225782356361301</v>
+        <v>0.07626398887290511</v>
       </c>
       <c r="L6" t="n">
-        <v>1.34277002378688</v>
+        <v>0.8794875026894234</v>
       </c>
       <c r="M6" t="n">
         <v>5</v>
@@ -775,17 +775,17 @@
   <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
@@ -860,7 +860,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.7075824164304918</v>
+        <v>0.4086956512454042</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2265145849180154</v>
+        <v>2.535338649478117</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1534632768361582</v>
+        <v>1.586123962213442</v>
       </c>
       <c r="H2" t="n">
-        <v>11.28813559322034</v>
+        <v>9.653121526592447</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05769637344403198</v>
+        <v>0.1243675999133593</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02264141774146809</v>
+        <v>0.2094044716037683</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01761644976276228</v>
+        <v>0.1161712416186803</v>
       </c>
       <c r="L2" t="n">
-        <v>1.091018728676065</v>
+        <v>0.8405404365051592</v>
       </c>
       <c r="M2" t="n">
         <v>5</v>
@@ -919,9 +919,9 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
@@ -973,16 +973,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7075824164304918</v>
+        <v>0.4086956512454042</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2265145849180154</v>
+        <v>2.535338649478117</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1534632768361582</v>
+        <v>1.586123962213442</v>
       </c>
       <c r="F2" t="n">
-        <v>11.28813559322034</v>
+        <v>9.653121526592447</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -998,16 +998,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.6891342697800888</v>
+        <v>0.3460798162399042</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2334507636116066</v>
+        <v>2.667324015363976</v>
       </c>
       <c r="E3" t="n">
-        <v>0.159833193145213</v>
+        <v>1.772661726891013</v>
       </c>
       <c r="F3" t="n">
-        <v>11.31896148721601</v>
+        <v>11.33148578435193</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -1023,16 +1023,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.631129215306083</v>
+        <v>0.309031006433505</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2542475858244539</v>
+        <v>2.740271040236071</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1745126960764377</v>
+        <v>1.733584190785634</v>
       </c>
       <c r="F4" t="n">
-        <v>12.65527712440974</v>
+        <v>10.7822156512856</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -1044,20 +1044,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6004528082484381</v>
+        <v>0.3067468478319929</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2642198828533087</v>
+        <v>2.745453465559433</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1424584300841315</v>
+        <v>1.705698004783789</v>
       </c>
       <c r="F5" t="n">
-        <v>10.3845632884462</v>
+        <v>10.33745886530554</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.599146075639495</v>
+        <v>0.2539176593976449</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2643673972632752</v>
+        <v>2.834278764941554</v>
       </c>
       <c r="E6" t="n">
-        <v>0.171090395480226</v>
+        <v>1.748594033518405</v>
       </c>
       <c r="F6" t="n">
-        <v>12.73135593220339</v>
+        <v>10.95046767711853</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -1103,12 +1103,12 @@
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -1152,7 +1152,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1164,22 +1164,22 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5096979117415289</v>
+        <v>0.1804339803759399</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2818508908455553</v>
+        <v>2.629641530865169</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1988135593220339</v>
+        <v>1.670272784810126</v>
       </c>
       <c r="G2" t="n">
-        <v>13.82344632768362</v>
+        <v>10.79708549791597</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1191,22 +1191,22 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0.514668423091825</v>
+        <v>0.4540148102991654</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2999378466689503</v>
+        <v>2.574259963834158</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1805649717514124</v>
+        <v>1.695220886075949</v>
       </c>
       <c r="G3" t="n">
-        <v>13.8093220338983</v>
+        <v>10.82287534938383</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1218,22 +1218,22 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5752523049645392</v>
+        <v>0.2124364417612893</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2623330784857232</v>
+        <v>2.691334071395398</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1653672316384181</v>
+        <v>1.605539240506328</v>
       </c>
       <c r="G4" t="n">
-        <v>12.50988700564972</v>
+        <v>9.328820891229274</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1245,22 +1245,22 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6759723271935036</v>
+        <v>0.2310288273644584</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2554909236210373</v>
+        <v>2.957841500985813</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1734180790960452</v>
+        <v>1.709174946921446</v>
       </c>
       <c r="G5" t="n">
-        <v>12.96327683615819</v>
+        <v>9.831839922883708</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1272,22 +1272,22 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7201394112060779</v>
+        <v>0.4558201793591112</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2222242466951098</v>
+        <v>2.874190260716625</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1372881355932203</v>
+        <v>1.848282165605095</v>
       </c>
       <c r="G6" t="n">
-        <v>10.55084745762712</v>
+        <v>10.90667266511492</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1299,22 +1299,22 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6641486603624902</v>
+        <v>0.3048644190586982</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2332711781622523</v>
+        <v>2.421805926458386</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1704519774011299</v>
+        <v>1.550302109704639</v>
       </c>
       <c r="G7" t="n">
-        <v>11.64406779661017</v>
+        <v>9.843944216650987</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1326,22 +1326,22 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6355832450815792</v>
+        <v>0.5736284432341305</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2599029226272901</v>
+        <v>2.274867383039044</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1657062146892656</v>
+        <v>1.495530590717299</v>
       </c>
       <c r="G8" t="n">
-        <v>12.35875706214689</v>
+        <v>9.732873186402296</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1353,22 +1353,22 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7153261623325453</v>
+        <v>0.3295128873893953</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2147639180347625</v>
+        <v>2.483247578118918</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1442372881355932</v>
+        <v>1.52712362869198</v>
       </c>
       <c r="G9" t="n">
-        <v>10.63983050847457</v>
+        <v>9.032422389165033</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1380,22 +1380,22 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7475225351554763</v>
+        <v>0.3243229942554524</v>
       </c>
       <c r="E10" t="n">
-        <v>0.225525542333504</v>
+        <v>2.772614169195625</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1595480225988701</v>
+        <v>1.569693842887474</v>
       </c>
       <c r="G10" t="n">
-        <v>12.07485875706215</v>
+        <v>8.747281942234538</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1407,22 +1407,22 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7753314792203682</v>
+        <v>0.5111495122893445</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1991093634322681</v>
+        <v>2.724158190578612</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1273728813559322</v>
+        <v>1.787969639065817</v>
       </c>
       <c r="G11" t="n">
-        <v>9.72316384180791</v>
+        <v>10.90908589850938</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1434,22 +1434,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5210533609048746</v>
+        <v>0.2244303858407491</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2785679225259067</v>
+        <v>2.558084999891274</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1710112115084115</v>
+        <v>1.637319457500796</v>
       </c>
       <c r="G12" t="n">
-        <v>11.13615627005949</v>
+        <v>10.62911113167301</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1461,22 +1461,22 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5908801533502738</v>
+        <v>0.4401404643386795</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2753830901183061</v>
+        <v>2.606762777899443</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1350980941521919</v>
+        <v>1.750241053511825</v>
       </c>
       <c r="G13" t="n">
-        <v>10.95348581419153</v>
+        <v>12.08900344685244</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1488,22 +1488,22 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5309857944042633</v>
+        <v>0.0002444106649146516</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2756643079434532</v>
+        <v>3.032296911864748</v>
       </c>
       <c r="F14" t="n">
-        <v>0.143752475411205</v>
+        <v>1.717943867671339</v>
       </c>
       <c r="G14" t="n">
-        <v>11.16535512067504</v>
+        <v>9.993065327400576</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1515,22 +1515,22 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0.689088351218363</v>
+        <v>0.135056470592115</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2502666166407419</v>
+        <v>3.136994415904676</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1361126823950622</v>
+        <v>1.811602405013552</v>
       </c>
       <c r="G15" t="n">
-        <v>9.110748161703853</v>
+        <v>10.40089834631426</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1542,22 +1542,22 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6702563813644158</v>
+        <v>0.4697165655517661</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2412174770381354</v>
+        <v>2.837254719147627</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1263176869537871</v>
+        <v>1.825863383894514</v>
       </c>
       <c r="G16" t="n">
-        <v>9.557071075601092</v>
+        <v>11.64026013335238</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1569,22 +1569,22 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6304427922362768</v>
+        <v>0.2041628169753197</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2446968501165838</v>
+        <v>2.591294011909131</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1775684001307204</v>
+        <v>1.687215136433737</v>
       </c>
       <c r="G17" t="n">
-        <v>11.69486161741834</v>
+        <v>11.13488069732751</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1596,22 +1596,22 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6476515300032419</v>
+        <v>0.3415600397450037</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2555631249789595</v>
+        <v>2.826962589194093</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1676182587655647</v>
+        <v>1.854904546065386</v>
       </c>
       <c r="G18" t="n">
-        <v>12.3492082015384</v>
+        <v>12.17063531987831</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1623,22 +1623,22 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6753266710911043</v>
+        <v>0.291494778772145</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2293563915689381</v>
+        <v>2.552679735615278</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1527719954896816</v>
+        <v>1.720678144777916</v>
       </c>
       <c r="G19" t="n">
-        <v>10.85019748437418</v>
+        <v>10.82354630243838</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1650,22 +1650,22 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7512134213950209</v>
+        <v>0.3671571014556091</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2238710309712114</v>
+        <v>2.683291309505526</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1632088341289259</v>
+        <v>1.783053139858087</v>
       </c>
       <c r="G20" t="n">
-        <v>11.64197758317975</v>
+        <v>10.9894516866725</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1677,22 +1677,22 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7410369341748004</v>
+        <v>0.5260243442514434</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2137664204223401</v>
+        <v>2.682392430595852</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1379984772111725</v>
+        <v>1.817457667319941</v>
       </c>
       <c r="G21" t="n">
-        <v>10.05856254956937</v>
+        <v>11.53891491544293</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1704,22 +1704,22 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5540882866801717</v>
+        <v>0.2354062491361637</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2687893027252355</v>
+        <v>2.539919488341214</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1989311682213938</v>
+        <v>1.677204805743682</v>
       </c>
       <c r="G22" t="n">
-        <v>13.63927893854905</v>
+        <v>10.97802838586767</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1731,22 +1731,22 @@
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6303479541754455</v>
+        <v>0.3502839191916148</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2617631764008746</v>
+        <v>2.808172481564636</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1749535940170056</v>
+        <v>1.780126195886957</v>
       </c>
       <c r="G23" t="n">
-        <v>12.93940970810529</v>
+        <v>11.76795529205565</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1758,22 +1758,22 @@
         <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5821788447193872</v>
+        <v>0.2254935400602559</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2601852982435431</v>
+        <v>2.668930873055173</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1750747792351021</v>
+        <v>1.69773798668779</v>
       </c>
       <c r="G24" t="n">
-        <v>12.95547232460194</v>
+        <v>10.40031128031047</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1785,22 +1785,22 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6702870787671645</v>
+        <v>0.2079839702666535</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2577225436645673</v>
+        <v>3.001835257963587</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1760539747411815</v>
+        <v>1.763263546307023</v>
       </c>
       <c r="G25" t="n">
-        <v>12.91772411483323</v>
+        <v>10.1705784377731</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1812,16 +1812,16 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.7187439121882457</v>
+        <v>0.5259873535128372</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2227776080880491</v>
+        <v>2.682497100255748</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1475499641675053</v>
+        <v>1.749588419302718</v>
       </c>
       <c r="G26" t="n">
-        <v>10.82450053595918</v>
+        <v>10.59420486042111</v>
       </c>
     </row>
   </sheetData>
@@ -1888,7 +1888,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16 17:02:47 UTC</t>
+          <t>2026-06-16 17:21:02 UTC</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/NN/reports/model_comparison.xlsx
+++ b/NN/reports/model_comparison.xlsx
@@ -565,16 +565,16 @@
         <v>9.653121526592447</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.1243675999133593</v>
+        <v>0.1243675999133594</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>0.2094044716037683</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.1161712416186803</v>
+        <v>0.1161712416186804</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.8405404365051592</v>
+        <v>0.8405404365051572</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>5</v>
@@ -694,7 +694,7 @@
         <v>2.745453465559433</v>
       </c>
       <c r="G5" t="n">
-        <v>1.705698004783789</v>
+        <v>1.705698004783788</v>
       </c>
       <c r="H5" t="n">
         <v>10.33745886530554</v>
@@ -706,10 +706,10 @@
         <v>0.1638065689272675</v>
       </c>
       <c r="K5" t="n">
-        <v>0.08907696999215506</v>
+        <v>0.08907696999215489</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7148236202024966</v>
+        <v>0.7148236202024981</v>
       </c>
       <c r="M5" t="n">
         <v>5</v>
@@ -887,16 +887,16 @@
         <v>9.653121526592447</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1243675999133593</v>
+        <v>0.1243675999133594</v>
       </c>
       <c r="J2" t="n">
         <v>0.2094044716037683</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1161712416186803</v>
+        <v>0.1161712416186804</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8405404365051592</v>
+        <v>0.8405404365051572</v>
       </c>
       <c r="M2" t="n">
         <v>5</v>
@@ -1054,7 +1054,7 @@
         <v>2.745453465559433</v>
       </c>
       <c r="E5" t="n">
-        <v>1.705698004783789</v>
+        <v>1.705698004783788</v>
       </c>
       <c r="F5" t="n">
         <v>10.33745886530554</v>
@@ -1170,7 +1170,7 @@
         <v>2.629641530865169</v>
       </c>
       <c r="F2" t="n">
-        <v>1.670272784810126</v>
+        <v>1.670272784810125</v>
       </c>
       <c r="G2" t="n">
         <v>10.79708549791597</v>
@@ -1227,7 +1227,7 @@
         <v>1.605539240506328</v>
       </c>
       <c r="G4" t="n">
-        <v>9.328820891229274</v>
+        <v>9.32882089122927</v>
       </c>
     </row>
     <row r="5">
@@ -1251,10 +1251,10 @@
         <v>2.957841500985813</v>
       </c>
       <c r="F5" t="n">
-        <v>1.709174946921446</v>
+        <v>1.709174946921445</v>
       </c>
       <c r="G5" t="n">
-        <v>9.831839922883708</v>
+        <v>9.831839922883706</v>
       </c>
     </row>
     <row r="6">
@@ -1278,7 +1278,7 @@
         <v>2.874190260716625</v>
       </c>
       <c r="F6" t="n">
-        <v>1.848282165605095</v>
+        <v>1.848282165605094</v>
       </c>
       <c r="G6" t="n">
         <v>10.90667266511492</v>
@@ -1299,7 +1299,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3048644190586982</v>
+        <v>0.3048644190586981</v>
       </c>
       <c r="E7" t="n">
         <v>2.421805926458386</v>
@@ -1308,7 +1308,7 @@
         <v>1.550302109704639</v>
       </c>
       <c r="G7" t="n">
-        <v>9.843944216650987</v>
+        <v>9.843944216650986</v>
       </c>
     </row>
     <row r="8">
@@ -1335,7 +1335,7 @@
         <v>1.495530590717299</v>
       </c>
       <c r="G8" t="n">
-        <v>9.732873186402296</v>
+        <v>9.732873186402292</v>
       </c>
     </row>
     <row r="9">
@@ -1353,16 +1353,16 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3295128873893953</v>
+        <v>0.3295128873893954</v>
       </c>
       <c r="E9" t="n">
         <v>2.483247578118918</v>
       </c>
       <c r="F9" t="n">
-        <v>1.52712362869198</v>
+        <v>1.527123628691981</v>
       </c>
       <c r="G9" t="n">
-        <v>9.032422389165033</v>
+        <v>9.032422389165037</v>
       </c>
     </row>
     <row r="10">
@@ -1380,7 +1380,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3243229942554524</v>
+        <v>0.3243229942554523</v>
       </c>
       <c r="E10" t="n">
         <v>2.772614169195625</v>
@@ -1389,7 +1389,7 @@
         <v>1.569693842887474</v>
       </c>
       <c r="G10" t="n">
-        <v>8.747281942234538</v>
+        <v>8.747281942234542</v>
       </c>
     </row>
     <row r="11">
@@ -1888,7 +1888,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16 17:21:02 UTC</t>
+          <t>2026-06-16 18:08:51 UTC</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/NN/reports/model_comparison.xlsx
+++ b/NN/reports/model_comparison.xlsx
@@ -457,7 +457,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -568,13 +568,13 @@
         <v>0.1243675999133594</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.2094044716037683</v>
+        <v>0.2094044716037686</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.1161712416186804</v>
+        <v>0.1161712416186803</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.8405404365051572</v>
+        <v>0.840540436505158</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>5</v>
@@ -694,22 +694,22 @@
         <v>2.745453465559433</v>
       </c>
       <c r="G5" t="n">
-        <v>1.705698004783788</v>
+        <v>1.705698004783789</v>
       </c>
       <c r="H5" t="n">
         <v>10.33745886530554</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1364673246088052</v>
+        <v>0.1364673246088053</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1638065689272675</v>
+        <v>0.1638065689272672</v>
       </c>
       <c r="K5" t="n">
-        <v>0.08907696999215489</v>
+        <v>0.08907696999215486</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7148236202024981</v>
+        <v>0.7148236202024966</v>
       </c>
       <c r="M5" t="n">
         <v>5</v>
@@ -783,10 +783,10 @@
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
@@ -890,13 +890,13 @@
         <v>0.1243675999133594</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2094044716037683</v>
+        <v>0.2094044716037686</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1161712416186804</v>
+        <v>0.1161712416186803</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8405404365051572</v>
+        <v>0.840540436505158</v>
       </c>
       <c r="M2" t="n">
         <v>5</v>
@@ -919,7 +919,7 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -1054,7 +1054,7 @@
         <v>2.745453465559433</v>
       </c>
       <c r="E5" t="n">
-        <v>1.705698004783788</v>
+        <v>1.705698004783789</v>
       </c>
       <c r="F5" t="n">
         <v>10.33745886530554</v>
@@ -1164,13 +1164,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1804339803759399</v>
+        <v>0.1804339803759398</v>
       </c>
       <c r="E2" t="n">
         <v>2.629641530865169</v>
       </c>
       <c r="F2" t="n">
-        <v>1.670272784810125</v>
+        <v>1.670272784810126</v>
       </c>
       <c r="G2" t="n">
         <v>10.79708549791597</v>
@@ -1191,7 +1191,7 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4540148102991654</v>
+        <v>0.4540148102991655</v>
       </c>
       <c r="E3" t="n">
         <v>2.574259963834158</v>
@@ -1227,7 +1227,7 @@
         <v>1.605539240506328</v>
       </c>
       <c r="G4" t="n">
-        <v>9.32882089122927</v>
+        <v>9.328820891229274</v>
       </c>
     </row>
     <row r="5">
@@ -1254,7 +1254,7 @@
         <v>1.709174946921445</v>
       </c>
       <c r="G5" t="n">
-        <v>9.831839922883706</v>
+        <v>9.831839922883704</v>
       </c>
     </row>
     <row r="6">
@@ -1272,7 +1272,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4558201793591112</v>
+        <v>0.4558201793591115</v>
       </c>
       <c r="E6" t="n">
         <v>2.874190260716625</v>
@@ -1329,13 +1329,13 @@
         <v>0.5736284432341305</v>
       </c>
       <c r="E8" t="n">
-        <v>2.274867383039044</v>
+        <v>2.274867383039043</v>
       </c>
       <c r="F8" t="n">
         <v>1.495530590717299</v>
       </c>
       <c r="G8" t="n">
-        <v>9.732873186402292</v>
+        <v>9.732873186402294</v>
       </c>
     </row>
     <row r="9">
@@ -1359,10 +1359,10 @@
         <v>2.483247578118918</v>
       </c>
       <c r="F9" t="n">
-        <v>1.527123628691981</v>
+        <v>1.52712362869198</v>
       </c>
       <c r="G9" t="n">
-        <v>9.032422389165037</v>
+        <v>9.032422389165033</v>
       </c>
     </row>
     <row r="10">
@@ -1380,10 +1380,10 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3243229942554523</v>
+        <v>0.3243229942554522</v>
       </c>
       <c r="E10" t="n">
-        <v>2.772614169195625</v>
+        <v>2.772614169195626</v>
       </c>
       <c r="F10" t="n">
         <v>1.569693842887474</v>
@@ -1407,10 +1407,10 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5111495122893445</v>
+        <v>0.5111495122893446</v>
       </c>
       <c r="E11" t="n">
-        <v>2.724158190578612</v>
+        <v>2.724158190578611</v>
       </c>
       <c r="F11" t="n">
         <v>1.787969639065817</v>
@@ -1888,7 +1888,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16 18:08:51 UTC</t>
+          <t>2026-06-16 19:01:08 UTC</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/NN/reports/model_comparison.xlsx
+++ b/NN/reports/model_comparison.xlsx
@@ -457,11 +457,11 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
@@ -553,28 +553,28 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.4765076752689186</v>
+        <v>0.5145843769405423</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2.411560166509476</v>
+        <v>2.324408554265008</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1.534844103509903</v>
+        <v>1.469392900104812</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9.698517973516919</v>
+        <v>9.156155169255126</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.0532260007112829</v>
+        <v>0.05547054150310089</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.3044464880315454</v>
+        <v>0.3326911062311046</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.1294739352122044</v>
+        <v>0.1440550240776139</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.8251772995582216</v>
+        <v>0.8165757686407464</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>5</v>
@@ -598,28 +598,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4408515721769954</v>
+        <v>0.4693202744333728</v>
       </c>
       <c r="F3" t="n">
-        <v>2.496458653689449</v>
+        <v>2.431822390292165</v>
       </c>
       <c r="G3" t="n">
-        <v>1.596568687890219</v>
+        <v>1.540545760434302</v>
       </c>
       <c r="H3" t="n">
-        <v>10.10424737583744</v>
+        <v>9.728131021221682</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08929621776651257</v>
+        <v>0.08802979849040111</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4197133664981815</v>
+        <v>0.4147953125467814</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1659924308846498</v>
+        <v>0.1536577359258704</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6679998713349482</v>
+        <v>0.6294274558814169</v>
       </c>
       <c r="M3" t="n">
         <v>5</v>
@@ -643,28 +643,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.4388202209456302</v>
+        <v>0.4528727854530306</v>
       </c>
       <c r="F4" t="n">
-        <v>2.493266719528956</v>
+        <v>2.455369244103912</v>
       </c>
       <c r="G4" t="n">
-        <v>1.625587415166397</v>
+        <v>1.616266828169435</v>
       </c>
       <c r="H4" t="n">
-        <v>10.5175527143969</v>
+        <v>10.40245184834743</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06998022441478449</v>
+        <v>0.07588795418503885</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3108560338679105</v>
+        <v>0.2419776457187243</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1447888080838037</v>
+        <v>0.09816228546697167</v>
       </c>
       <c r="L4" t="n">
-        <v>0.876721359005583</v>
+        <v>0.5789204230913501</v>
       </c>
       <c r="M4" t="n">
         <v>5</v>
@@ -688,28 +688,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.4093377555016319</v>
+        <v>0.4041066691564266</v>
       </c>
       <c r="F5" t="n">
-        <v>2.55086904063175</v>
+        <v>2.56125358609114</v>
       </c>
       <c r="G5" t="n">
-        <v>1.766342309897531</v>
+        <v>1.722720249009499</v>
       </c>
       <c r="H5" t="n">
-        <v>11.53482859524611</v>
+        <v>11.07068904226662</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07758407243283573</v>
+        <v>0.06974896813083979</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2350186167615563</v>
+        <v>0.1879798155985191</v>
       </c>
       <c r="K5" t="n">
-        <v>0.107096557123969</v>
+        <v>0.1141711970306861</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8681846242125181</v>
+        <v>0.8095514614440562</v>
       </c>
       <c r="M5" t="n">
         <v>5</v>
@@ -733,28 +733,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.3345282627238162</v>
+        <v>0.4012945541335625</v>
       </c>
       <c r="F6" t="n">
-        <v>2.701491283093353</v>
+        <v>2.56466168751983</v>
       </c>
       <c r="G6" t="n">
-        <v>1.714295529055329</v>
+        <v>1.604388690086644</v>
       </c>
       <c r="H6" t="n">
-        <v>11.09118254822936</v>
+        <v>10.21126081730861</v>
       </c>
       <c r="I6" t="n">
-        <v>0.130292270355815</v>
+        <v>0.1112647802768699</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3274730188216585</v>
+        <v>0.3211165637487183</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1411293970243854</v>
+        <v>0.1183153972470814</v>
       </c>
       <c r="L6" t="n">
-        <v>1.097335947280984</v>
+        <v>0.7512904023338809</v>
       </c>
       <c r="M6" t="n">
         <v>5</v>
@@ -779,12 +779,12 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.4765076752689186</v>
+        <v>0.5145843769405423</v>
       </c>
       <c r="F2" t="n">
-        <v>2.411560166509476</v>
+        <v>2.324408554265008</v>
       </c>
       <c r="G2" t="n">
-        <v>1.534844103509903</v>
+        <v>1.469392900104812</v>
       </c>
       <c r="H2" t="n">
-        <v>9.698517973516919</v>
+        <v>9.156155169255126</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0532260007112829</v>
+        <v>0.05547054150310089</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3044464880315454</v>
+        <v>0.3326911062311046</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1294739352122044</v>
+        <v>0.1440550240776139</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8251772995582216</v>
+        <v>0.8165757686407464</v>
       </c>
       <c r="M2" t="n">
         <v>5</v>
@@ -919,7 +919,7 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -973,16 +973,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4765076752689186</v>
+        <v>0.5145843769405423</v>
       </c>
       <c r="D2" t="n">
-        <v>2.411560166509476</v>
+        <v>2.324408554265008</v>
       </c>
       <c r="E2" t="n">
-        <v>1.534844103509903</v>
+        <v>1.469392900104812</v>
       </c>
       <c r="F2" t="n">
-        <v>9.698517973516919</v>
+        <v>9.156155169255126</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -998,16 +998,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.4408515721769954</v>
+        <v>0.4693202744333728</v>
       </c>
       <c r="D3" t="n">
-        <v>2.496458653689449</v>
+        <v>2.431822390292165</v>
       </c>
       <c r="E3" t="n">
-        <v>1.596568687890219</v>
+        <v>1.540545760434302</v>
       </c>
       <c r="F3" t="n">
-        <v>10.10424737583744</v>
+        <v>9.728131021221682</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -1023,16 +1023,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.4388202209456302</v>
+        <v>0.4528727854530306</v>
       </c>
       <c r="D4" t="n">
-        <v>2.493266719528956</v>
+        <v>2.455369244103912</v>
       </c>
       <c r="E4" t="n">
-        <v>1.625587415166397</v>
+        <v>1.616266828169435</v>
       </c>
       <c r="F4" t="n">
-        <v>10.5175527143969</v>
+        <v>10.40245184834743</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -1048,16 +1048,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.4093377555016319</v>
+        <v>0.4041066691564266</v>
       </c>
       <c r="D5" t="n">
-        <v>2.55086904063175</v>
+        <v>2.56125358609114</v>
       </c>
       <c r="E5" t="n">
-        <v>1.766342309897531</v>
+        <v>1.722720249009499</v>
       </c>
       <c r="F5" t="n">
-        <v>11.53482859524611</v>
+        <v>11.07068904226662</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.3345282627238162</v>
+        <v>0.4012945541335625</v>
       </c>
       <c r="D6" t="n">
-        <v>2.701491283093353</v>
+        <v>2.56466168751983</v>
       </c>
       <c r="E6" t="n">
-        <v>1.714295529055329</v>
+        <v>1.604388690086644</v>
       </c>
       <c r="F6" t="n">
-        <v>11.09118254822936</v>
+        <v>10.21126081730861</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -1164,16 +1164,16 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3661937960470624</v>
+        <v>0.4015377454027587</v>
       </c>
       <c r="E2" t="n">
-        <v>2.312505749809305</v>
+        <v>2.247102901284053</v>
       </c>
       <c r="F2" t="n">
-        <v>1.545371187191988</v>
+        <v>1.47646540084388</v>
       </c>
       <c r="G2" t="n">
-        <v>10.40183769171498</v>
+        <v>9.922465910465334</v>
       </c>
     </row>
     <row r="3">
@@ -1191,16 +1191,16 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4921235294267304</v>
+        <v>0.526154792462501</v>
       </c>
       <c r="E3" t="n">
-        <v>2.48279588934721</v>
+        <v>2.398171389668895</v>
       </c>
       <c r="F3" t="n">
-        <v>1.610253412237118</v>
+        <v>1.530081645569619</v>
       </c>
       <c r="G3" t="n">
-        <v>9.956950329181975</v>
+        <v>9.410586514416016</v>
       </c>
     </row>
     <row r="4">
@@ -1218,16 +1218,16 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5609748691944558</v>
+        <v>0.5904034131806324</v>
       </c>
       <c r="E4" t="n">
-        <v>2.009414323653141</v>
+        <v>1.940899140532581</v>
       </c>
       <c r="F4" t="n">
-        <v>1.438499018169184</v>
+        <v>1.39386434599156</v>
       </c>
       <c r="G4" t="n">
-        <v>9.550552752519167</v>
+        <v>9.249174606340071</v>
       </c>
     </row>
     <row r="5">
@@ -1245,16 +1245,16 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.440357589338596</v>
+        <v>0.4492266175267953</v>
       </c>
       <c r="E5" t="n">
-        <v>2.523336547052147</v>
+        <v>2.50326219417127</v>
       </c>
       <c r="F5" t="n">
-        <v>1.516464962158538</v>
+        <v>1.502428874734609</v>
       </c>
       <c r="G5" t="n">
-        <v>9.503858645705247</v>
+        <v>9.309695478537982</v>
       </c>
     </row>
     <row r="6">
@@ -1272,16 +1272,16 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3446080768781326</v>
+        <v>0.3792788035941768</v>
       </c>
       <c r="E6" t="n">
-        <v>3.154240758585444</v>
+        <v>3.069676325804024</v>
       </c>
       <c r="F6" t="n">
-        <v>1.872254859694268</v>
+        <v>1.799888535031845</v>
       </c>
       <c r="G6" t="n">
-        <v>11.10803746006581</v>
+        <v>10.748732596349</v>
       </c>
     </row>
     <row r="7">
@@ -1299,16 +1299,16 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.417362163119355</v>
+        <v>0.4921050851862888</v>
       </c>
       <c r="E7" t="n">
-        <v>2.217195153270039</v>
+        <v>2.070100882792117</v>
       </c>
       <c r="F7" t="n">
-        <v>1.461699314345989</v>
+        <v>1.348342616033752</v>
       </c>
       <c r="G7" t="n">
-        <v>9.669592453056524</v>
+        <v>8.850431925043637</v>
       </c>
     </row>
     <row r="8">
@@ -1326,16 +1326,16 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5494097054474665</v>
+        <v>0.6022918301486293</v>
       </c>
       <c r="E8" t="n">
-        <v>2.338583535539986</v>
+        <v>2.197071686983065</v>
       </c>
       <c r="F8" t="n">
-        <v>1.507964135021097</v>
+        <v>1.422623839662447</v>
       </c>
       <c r="G8" t="n">
-        <v>9.786398256157359</v>
+        <v>9.136907946025028</v>
       </c>
     </row>
     <row r="9">
@@ -1353,16 +1353,16 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5119710041894012</v>
+        <v>0.5324335348160026</v>
       </c>
       <c r="E9" t="n">
-        <v>2.118593405923864</v>
+        <v>2.073702641042575</v>
       </c>
       <c r="F9" t="n">
-        <v>1.453856962025314</v>
+        <v>1.430940295358648</v>
       </c>
       <c r="G9" t="n">
-        <v>9.175101638224193</v>
+        <v>8.993695474295887</v>
       </c>
     </row>
     <row r="10">
@@ -1380,16 +1380,16 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4569070746174353</v>
+        <v>0.4860936110184395</v>
       </c>
       <c r="E10" t="n">
-        <v>2.485747099407418</v>
+        <v>2.418031070610126</v>
       </c>
       <c r="F10" t="n">
-        <v>1.487437515923568</v>
+        <v>1.425195541401273</v>
       </c>
       <c r="G10" t="n">
-        <v>8.850636789832791</v>
+        <v>8.298017367358989</v>
       </c>
     </row>
     <row r="11">
@@ -1407,16 +1407,16 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4468884289709351</v>
+        <v>0.4599978235333507</v>
       </c>
       <c r="E11" t="n">
-        <v>2.897681638406072</v>
+        <v>2.863136489897156</v>
       </c>
       <c r="F11" t="n">
-        <v>1.763262590233544</v>
+        <v>1.719862208067939</v>
       </c>
       <c r="G11" t="n">
-        <v>11.01086073031373</v>
+        <v>10.50172313355208</v>
       </c>
     </row>
     <row r="12">
@@ -1434,16 +1434,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2466817044568479</v>
+        <v>0.3391971885866912</v>
       </c>
       <c r="E12" t="n">
-        <v>2.521121846931162</v>
+        <v>2.361242107523141</v>
       </c>
       <c r="F12" t="n">
-        <v>1.726586229042917</v>
+        <v>1.519681488743311</v>
       </c>
       <c r="G12" t="n">
-        <v>12.02141174942526</v>
+        <v>10.2263668811902</v>
       </c>
     </row>
     <row r="13">
@@ -1461,16 +1461,16 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4854850393527227</v>
+        <v>0.5613640609441286</v>
       </c>
       <c r="E13" t="n">
-        <v>2.498969611270043</v>
+        <v>2.307353187896521</v>
       </c>
       <c r="F13" t="n">
-        <v>1.638364736570187</v>
+        <v>1.529611498274475</v>
       </c>
       <c r="G13" t="n">
-        <v>10.67477652803051</v>
+        <v>10.01857004224986</v>
       </c>
     </row>
     <row r="14">
@@ -1488,16 +1488,16 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1862107655493713</v>
+        <v>0.2796470998064836</v>
       </c>
       <c r="E14" t="n">
-        <v>2.735777499606052</v>
+        <v>2.57393430260522</v>
       </c>
       <c r="F14" t="n">
-        <v>1.645973095079011</v>
+        <v>1.620011617322511</v>
       </c>
       <c r="G14" t="n">
-        <v>10.02780513329258</v>
+        <v>9.92482676321551</v>
       </c>
     </row>
     <row r="15">
@@ -1515,16 +1515,16 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0.453849294222548</v>
+        <v>0.4629454224329047</v>
       </c>
       <c r="E15" t="n">
-        <v>2.492735037933065</v>
+        <v>2.471889654535175</v>
       </c>
       <c r="F15" t="n">
-        <v>1.606526294331642</v>
+        <v>1.5485793393129</v>
       </c>
       <c r="G15" t="n">
-        <v>10.24880078443368</v>
+        <v>9.435626916834176</v>
       </c>
     </row>
     <row r="16">
@@ -1542,16 +1542,16 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3004145100375909</v>
+        <v>0.3633189988976043</v>
       </c>
       <c r="E16" t="n">
-        <v>3.258852419726442</v>
+        <v>3.108889185039096</v>
       </c>
       <c r="F16" t="n">
-        <v>1.954027290252886</v>
+        <v>1.804059506780023</v>
       </c>
       <c r="G16" t="n">
-        <v>12.48311854596476</v>
+        <v>11.45091348305329</v>
       </c>
     </row>
     <row r="17">
@@ -1569,16 +1569,16 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3274929375142605</v>
+        <v>0.3363215730070706</v>
       </c>
       <c r="E17" t="n">
-        <v>2.382061681844692</v>
+        <v>2.366374238823536</v>
       </c>
       <c r="F17" t="n">
-        <v>1.750001852170618</v>
+        <v>1.591060840532472</v>
       </c>
       <c r="G17" t="n">
-        <v>11.94566602545771</v>
+        <v>10.57986722665282</v>
       </c>
     </row>
     <row r="18">
@@ -1596,16 +1596,16 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4513700056554267</v>
+        <v>0.4638000330871673</v>
       </c>
       <c r="E18" t="n">
-        <v>2.580487412482213</v>
+        <v>2.55108754638635</v>
       </c>
       <c r="F18" t="n">
-        <v>1.800309644768467</v>
+        <v>1.776180592898495</v>
       </c>
       <c r="G18" t="n">
-        <v>11.94550649964226</v>
+        <v>11.66768665646218</v>
       </c>
     </row>
     <row r="19">
@@ -1623,16 +1623,16 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3325680303804825</v>
+        <v>0.3203747054320681</v>
       </c>
       <c r="E19" t="n">
-        <v>2.477583532976815</v>
+        <v>2.500112608568134</v>
       </c>
       <c r="F19" t="n">
-        <v>1.817210665169984</v>
+        <v>1.78514571015618</v>
       </c>
       <c r="G19" t="n">
-        <v>12.12646373167338</v>
+        <v>11.74069759972516</v>
       </c>
     </row>
     <row r="20">
@@ -1650,16 +1650,16 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5058556117916981</v>
+        <v>0.4439062366013358</v>
       </c>
       <c r="E20" t="n">
-        <v>2.371083249075643</v>
+        <v>2.515323688149471</v>
       </c>
       <c r="F20" t="n">
-        <v>1.591516402701223</v>
+        <v>1.612440432698072</v>
       </c>
       <c r="G20" t="n">
-        <v>10.0130830799387</v>
+        <v>9.884461686310214</v>
       </c>
     </row>
     <row r="21">
@@ -1677,16 +1677,16 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4294021921662918</v>
+        <v>0.4561307976544915</v>
       </c>
       <c r="E21" t="n">
-        <v>2.94312932677939</v>
+        <v>2.873369848528209</v>
       </c>
       <c r="F21" t="n">
-        <v>1.872672984677363</v>
+        <v>1.848773668762279</v>
       </c>
       <c r="G21" t="n">
-        <v>11.64342363951849</v>
+        <v>11.48073204218273</v>
       </c>
     </row>
     <row r="22">
@@ -1704,16 +1704,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3554489229980099</v>
+        <v>0.3372961985579841</v>
       </c>
       <c r="E22" t="n">
-        <v>2.332025244907385</v>
+        <v>2.364636065600208</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6303785324707</v>
+        <v>1.610978207194598</v>
       </c>
       <c r="G22" t="n">
-        <v>11.16083627093857</v>
+        <v>10.82854740139946</v>
       </c>
     </row>
     <row r="23">
@@ -1731,16 +1731,16 @@
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>0.534076328776136</v>
+        <v>0.5493056142525183</v>
       </c>
       <c r="E23" t="n">
-        <v>2.378041114165839</v>
+        <v>2.338853638891928</v>
       </c>
       <c r="F23" t="n">
-        <v>1.613236220192948</v>
+        <v>1.625921075521627</v>
       </c>
       <c r="G23" t="n">
-        <v>10.64391890958581</v>
+        <v>10.6114096453814</v>
       </c>
     </row>
     <row r="24">
@@ -1758,16 +1758,16 @@
         <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4370769714601126</v>
+        <v>0.4486943163963046</v>
       </c>
       <c r="E24" t="n">
-        <v>2.275355766200653</v>
+        <v>2.251754493728487</v>
       </c>
       <c r="F24" t="n">
-        <v>1.54779774834892</v>
+        <v>1.54304571975113</v>
       </c>
       <c r="G24" t="n">
-        <v>10.04911682515822</v>
+        <v>10.19277402867325</v>
       </c>
     </row>
     <row r="25">
@@ -1785,16 +1785,16 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4756419418281129</v>
+        <v>0.4712146815302456</v>
       </c>
       <c r="E25" t="n">
-        <v>2.442495891233774</v>
+        <v>2.452785459113523</v>
       </c>
       <c r="F25" t="n">
-        <v>1.475926425884253</v>
+        <v>1.526819039469361</v>
       </c>
       <c r="G25" t="n">
-        <v>9.276078665180689</v>
+        <v>9.489429275775372</v>
       </c>
     </row>
     <row r="26">
@@ -1812,16 +1812,16 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3918569396657796</v>
+        <v>0.4578531165281005</v>
       </c>
       <c r="E26" t="n">
-        <v>3.038415581137128</v>
+        <v>2.868816563185415</v>
       </c>
       <c r="F26" t="n">
-        <v>1.860598148935164</v>
+        <v>1.774570098910459</v>
       </c>
       <c r="G26" t="n">
-        <v>11.45781290112121</v>
+        <v>10.89009889050769</v>
       </c>
     </row>
   </sheetData>
@@ -1888,7 +1888,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-14 22:03:48 UTC</t>
+          <t>2026-06-16 19:28:16 UTC</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/NN/reports/model_comparison.xlsx
+++ b/NN/reports/model_comparison.xlsx
@@ -457,11 +457,11 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
@@ -553,28 +553,28 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.5145843769405423</v>
+        <v>0.4086956512454042</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2.324408554265008</v>
+        <v>2.535338649478117</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1.469392900104812</v>
+        <v>1.586123962213442</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9.156155169255126</v>
+        <v>9.653121526592447</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.05547054150310089</v>
+        <v>0.1243675999133594</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.3326911062311046</v>
+        <v>0.2094044716037683</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.1440550240776139</v>
+        <v>0.1161712416186803</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.8165757686407464</v>
+        <v>0.8405404365051589</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>5</v>
@@ -594,32 +594,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4693202744333728</v>
+        <v>0.3460798162399042</v>
       </c>
       <c r="F3" t="n">
-        <v>2.431822390292165</v>
+        <v>2.667324015363976</v>
       </c>
       <c r="G3" t="n">
-        <v>1.540545760434302</v>
+        <v>1.772661726891013</v>
       </c>
       <c r="H3" t="n">
-        <v>9.728131021221682</v>
+        <v>11.33148578435193</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08802979849040111</v>
+        <v>0.1182842703918661</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4147953125467814</v>
+        <v>0.1059367242493817</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1536577359258704</v>
+        <v>0.06870580702931066</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6294274558814169</v>
+        <v>0.5387119334359428</v>
       </c>
       <c r="M3" t="n">
         <v>5</v>
@@ -643,28 +643,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.4528727854530306</v>
+        <v>0.309031006433505</v>
       </c>
       <c r="F4" t="n">
-        <v>2.455369244103912</v>
+        <v>2.740271040236071</v>
       </c>
       <c r="G4" t="n">
-        <v>1.616266828169435</v>
+        <v>1.733584190785634</v>
       </c>
       <c r="H4" t="n">
-        <v>10.40245184834743</v>
+        <v>10.7822156512856</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07588795418503885</v>
+        <v>0.1335865599922902</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2419776457187243</v>
+        <v>0.1743519699278086</v>
       </c>
       <c r="K4" t="n">
-        <v>0.09816228546697167</v>
+        <v>0.0440645637655039</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5789204230913501</v>
+        <v>0.6255646156502747</v>
       </c>
       <c r="M4" t="n">
         <v>5</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.4041066691564266</v>
+        <v>0.3067468478319929</v>
       </c>
       <c r="F5" t="n">
-        <v>2.56125358609114</v>
+        <v>2.745453465559433</v>
       </c>
       <c r="G5" t="n">
-        <v>1.722720249009499</v>
+        <v>1.705698004783789</v>
       </c>
       <c r="H5" t="n">
-        <v>11.07068904226662</v>
+        <v>10.33745886530554</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06974896813083979</v>
+        <v>0.1364673246088053</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1879798155985191</v>
+        <v>0.1638065689272672</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1141711970306861</v>
+        <v>0.08907696999215509</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8095514614440562</v>
+        <v>0.7148236202024979</v>
       </c>
       <c r="M5" t="n">
         <v>5</v>
@@ -733,28 +733,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.4012945541335625</v>
+        <v>0.2539176593976449</v>
       </c>
       <c r="F6" t="n">
-        <v>2.56466168751983</v>
+        <v>2.834278764941554</v>
       </c>
       <c r="G6" t="n">
-        <v>1.604388690086644</v>
+        <v>1.748594033518405</v>
       </c>
       <c r="H6" t="n">
-        <v>10.21126081730861</v>
+        <v>10.95046767711853</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1112647802768699</v>
+        <v>0.2003719663564008</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3211165637487183</v>
+        <v>0.2544127199870098</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1183153972470814</v>
+        <v>0.07626398887290511</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7512904023338809</v>
+        <v>0.8794875026894234</v>
       </c>
       <c r="M6" t="n">
         <v>5</v>
@@ -780,11 +780,11 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.5145843769405423</v>
+        <v>0.4086956512454042</v>
       </c>
       <c r="F2" t="n">
-        <v>2.324408554265008</v>
+        <v>2.535338649478117</v>
       </c>
       <c r="G2" t="n">
-        <v>1.469392900104812</v>
+        <v>1.586123962213442</v>
       </c>
       <c r="H2" t="n">
-        <v>9.156155169255126</v>
+        <v>9.653121526592447</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05547054150310089</v>
+        <v>0.1243675999133594</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3326911062311046</v>
+        <v>0.2094044716037683</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1440550240776139</v>
+        <v>0.1161712416186803</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8165757686407464</v>
+        <v>0.8405404365051589</v>
       </c>
       <c r="M2" t="n">
         <v>5</v>
@@ -919,7 +919,7 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -973,16 +973,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5145843769405423</v>
+        <v>0.4086956512454042</v>
       </c>
       <c r="D2" t="n">
-        <v>2.324408554265008</v>
+        <v>2.535338649478117</v>
       </c>
       <c r="E2" t="n">
-        <v>1.469392900104812</v>
+        <v>1.586123962213442</v>
       </c>
       <c r="F2" t="n">
-        <v>9.156155169255126</v>
+        <v>9.653121526592447</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -994,20 +994,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.4693202744333728</v>
+        <v>0.3460798162399042</v>
       </c>
       <c r="D3" t="n">
-        <v>2.431822390292165</v>
+        <v>2.667324015363976</v>
       </c>
       <c r="E3" t="n">
-        <v>1.540545760434302</v>
+        <v>1.772661726891013</v>
       </c>
       <c r="F3" t="n">
-        <v>9.728131021221682</v>
+        <v>11.33148578435193</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -1023,16 +1023,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.4528727854530306</v>
+        <v>0.309031006433505</v>
       </c>
       <c r="D4" t="n">
-        <v>2.455369244103912</v>
+        <v>2.740271040236071</v>
       </c>
       <c r="E4" t="n">
-        <v>1.616266828169435</v>
+        <v>1.733584190785634</v>
       </c>
       <c r="F4" t="n">
-        <v>10.40245184834743</v>
+        <v>10.7822156512856</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -1044,20 +1044,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.4041066691564266</v>
+        <v>0.3067468478319929</v>
       </c>
       <c r="D5" t="n">
-        <v>2.56125358609114</v>
+        <v>2.745453465559433</v>
       </c>
       <c r="E5" t="n">
-        <v>1.722720249009499</v>
+        <v>1.705698004783789</v>
       </c>
       <c r="F5" t="n">
-        <v>11.07068904226662</v>
+        <v>10.33745886530554</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.4012945541335625</v>
+        <v>0.2539176593976449</v>
       </c>
       <c r="D6" t="n">
-        <v>2.56466168751983</v>
+        <v>2.834278764941554</v>
       </c>
       <c r="E6" t="n">
-        <v>1.604388690086644</v>
+        <v>1.748594033518405</v>
       </c>
       <c r="F6" t="n">
-        <v>10.21126081730861</v>
+        <v>10.95046767711853</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -1106,7 +1106,7 @@
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
@@ -1164,16 +1164,16 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4015377454027587</v>
+        <v>0.1804339803759399</v>
       </c>
       <c r="E2" t="n">
-        <v>2.247102901284053</v>
+        <v>2.629641530865169</v>
       </c>
       <c r="F2" t="n">
-        <v>1.47646540084388</v>
+        <v>1.670272784810126</v>
       </c>
       <c r="G2" t="n">
-        <v>9.922465910465334</v>
+        <v>10.79708549791597</v>
       </c>
     </row>
     <row r="3">
@@ -1191,16 +1191,16 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0.526154792462501</v>
+        <v>0.4540148102991655</v>
       </c>
       <c r="E3" t="n">
-        <v>2.398171389668895</v>
+        <v>2.574259963834158</v>
       </c>
       <c r="F3" t="n">
-        <v>1.530081645569619</v>
+        <v>1.695220886075949</v>
       </c>
       <c r="G3" t="n">
-        <v>9.410586514416016</v>
+        <v>10.82287534938383</v>
       </c>
     </row>
     <row r="4">
@@ -1218,16 +1218,16 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5904034131806324</v>
+        <v>0.2124364417612892</v>
       </c>
       <c r="E4" t="n">
-        <v>1.940899140532581</v>
+        <v>2.691334071395398</v>
       </c>
       <c r="F4" t="n">
-        <v>1.39386434599156</v>
+        <v>1.605539240506328</v>
       </c>
       <c r="G4" t="n">
-        <v>9.249174606340071</v>
+        <v>9.328820891229272</v>
       </c>
     </row>
     <row r="5">
@@ -1245,16 +1245,16 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4492266175267953</v>
+        <v>0.2310288273644584</v>
       </c>
       <c r="E5" t="n">
-        <v>2.50326219417127</v>
+        <v>2.957841500985813</v>
       </c>
       <c r="F5" t="n">
-        <v>1.502428874734609</v>
+        <v>1.709174946921445</v>
       </c>
       <c r="G5" t="n">
-        <v>9.309695478537982</v>
+        <v>9.831839922883704</v>
       </c>
     </row>
     <row r="6">
@@ -1272,16 +1272,16 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3792788035941768</v>
+        <v>0.4558201793591112</v>
       </c>
       <c r="E6" t="n">
-        <v>3.069676325804024</v>
+        <v>2.874190260716625</v>
       </c>
       <c r="F6" t="n">
-        <v>1.799888535031845</v>
+        <v>1.848282165605095</v>
       </c>
       <c r="G6" t="n">
-        <v>10.748732596349</v>
+        <v>10.90667266511492</v>
       </c>
     </row>
     <row r="7">
@@ -1299,16 +1299,16 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4921050851862888</v>
+        <v>0.3048644190586981</v>
       </c>
       <c r="E7" t="n">
-        <v>2.070100882792117</v>
+        <v>2.421805926458386</v>
       </c>
       <c r="F7" t="n">
-        <v>1.348342616033752</v>
+        <v>1.550302109704639</v>
       </c>
       <c r="G7" t="n">
-        <v>8.850431925043637</v>
+        <v>9.843944216650987</v>
       </c>
     </row>
     <row r="8">
@@ -1326,16 +1326,16 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6022918301486293</v>
+        <v>0.5736284432341305</v>
       </c>
       <c r="E8" t="n">
-        <v>2.197071686983065</v>
+        <v>2.274867383039044</v>
       </c>
       <c r="F8" t="n">
-        <v>1.422623839662447</v>
+        <v>1.495530590717299</v>
       </c>
       <c r="G8" t="n">
-        <v>9.136907946025028</v>
+        <v>9.732873186402296</v>
       </c>
     </row>
     <row r="9">
@@ -1353,16 +1353,16 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5324335348160026</v>
+        <v>0.3295128873893954</v>
       </c>
       <c r="E9" t="n">
-        <v>2.073702641042575</v>
+        <v>2.483247578118918</v>
       </c>
       <c r="F9" t="n">
-        <v>1.430940295358648</v>
+        <v>1.52712362869198</v>
       </c>
       <c r="G9" t="n">
-        <v>8.993695474295887</v>
+        <v>9.032422389165033</v>
       </c>
     </row>
     <row r="10">
@@ -1380,16 +1380,16 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4860936110184395</v>
+        <v>0.3243229942554522</v>
       </c>
       <c r="E10" t="n">
-        <v>2.418031070610126</v>
+        <v>2.772614169195626</v>
       </c>
       <c r="F10" t="n">
-        <v>1.425195541401273</v>
+        <v>1.569693842887474</v>
       </c>
       <c r="G10" t="n">
-        <v>8.298017367358989</v>
+        <v>8.74728194223454</v>
       </c>
     </row>
     <row r="11">
@@ -1407,16 +1407,16 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4599978235333507</v>
+        <v>0.5111495122893446</v>
       </c>
       <c r="E11" t="n">
-        <v>2.863136489897156</v>
+        <v>2.724158190578611</v>
       </c>
       <c r="F11" t="n">
-        <v>1.719862208067939</v>
+        <v>1.787969639065817</v>
       </c>
       <c r="G11" t="n">
-        <v>10.50172313355208</v>
+        <v>10.90908589850938</v>
       </c>
     </row>
     <row r="12">
@@ -1434,16 +1434,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3391971885866912</v>
+        <v>0.2244303858407491</v>
       </c>
       <c r="E12" t="n">
-        <v>2.361242107523141</v>
+        <v>2.558084999891274</v>
       </c>
       <c r="F12" t="n">
-        <v>1.519681488743311</v>
+        <v>1.637319457500796</v>
       </c>
       <c r="G12" t="n">
-        <v>10.2263668811902</v>
+        <v>10.62911113167301</v>
       </c>
     </row>
     <row r="13">
@@ -1461,16 +1461,16 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5613640609441286</v>
+        <v>0.4401404643386795</v>
       </c>
       <c r="E13" t="n">
-        <v>2.307353187896521</v>
+        <v>2.606762777899443</v>
       </c>
       <c r="F13" t="n">
-        <v>1.529611498274475</v>
+        <v>1.750241053511825</v>
       </c>
       <c r="G13" t="n">
-        <v>10.01857004224986</v>
+        <v>12.08900344685244</v>
       </c>
     </row>
     <row r="14">
@@ -1488,16 +1488,16 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2796470998064836</v>
+        <v>0.0002444106649146516</v>
       </c>
       <c r="E14" t="n">
-        <v>2.57393430260522</v>
+        <v>3.032296911864748</v>
       </c>
       <c r="F14" t="n">
-        <v>1.620011617322511</v>
+        <v>1.717943867671339</v>
       </c>
       <c r="G14" t="n">
-        <v>9.92482676321551</v>
+        <v>9.993065327400576</v>
       </c>
     </row>
     <row r="15">
@@ -1515,16 +1515,16 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4629454224329047</v>
+        <v>0.135056470592115</v>
       </c>
       <c r="E15" t="n">
-        <v>2.471889654535175</v>
+        <v>3.136994415904676</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5485793393129</v>
+        <v>1.811602405013552</v>
       </c>
       <c r="G15" t="n">
-        <v>9.435626916834176</v>
+        <v>10.40089834631426</v>
       </c>
     </row>
     <row r="16">
@@ -1542,16 +1542,16 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3633189988976043</v>
+        <v>0.4697165655517661</v>
       </c>
       <c r="E16" t="n">
-        <v>3.108889185039096</v>
+        <v>2.837254719147627</v>
       </c>
       <c r="F16" t="n">
-        <v>1.804059506780023</v>
+        <v>1.825863383894514</v>
       </c>
       <c r="G16" t="n">
-        <v>11.45091348305329</v>
+        <v>11.64026013335238</v>
       </c>
     </row>
     <row r="17">
@@ -1569,16 +1569,16 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3363215730070706</v>
+        <v>0.2041628169753197</v>
       </c>
       <c r="E17" t="n">
-        <v>2.366374238823536</v>
+        <v>2.591294011909131</v>
       </c>
       <c r="F17" t="n">
-        <v>1.591060840532472</v>
+        <v>1.687215136433737</v>
       </c>
       <c r="G17" t="n">
-        <v>10.57986722665282</v>
+        <v>11.13488069732751</v>
       </c>
     </row>
     <row r="18">
@@ -1596,16 +1596,16 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4638000330871673</v>
+        <v>0.3415600397450037</v>
       </c>
       <c r="E18" t="n">
-        <v>2.55108754638635</v>
+        <v>2.826962589194093</v>
       </c>
       <c r="F18" t="n">
-        <v>1.776180592898495</v>
+        <v>1.854904546065386</v>
       </c>
       <c r="G18" t="n">
-        <v>11.66768665646218</v>
+        <v>12.17063531987831</v>
       </c>
     </row>
     <row r="19">
@@ -1623,16 +1623,16 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3203747054320681</v>
+        <v>0.291494778772145</v>
       </c>
       <c r="E19" t="n">
-        <v>2.500112608568134</v>
+        <v>2.552679735615278</v>
       </c>
       <c r="F19" t="n">
-        <v>1.78514571015618</v>
+        <v>1.720678144777916</v>
       </c>
       <c r="G19" t="n">
-        <v>11.74069759972516</v>
+        <v>10.82354630243838</v>
       </c>
     </row>
     <row r="20">
@@ -1650,16 +1650,16 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4439062366013358</v>
+        <v>0.3671571014556091</v>
       </c>
       <c r="E20" t="n">
-        <v>2.515323688149471</v>
+        <v>2.683291309505526</v>
       </c>
       <c r="F20" t="n">
-        <v>1.612440432698072</v>
+        <v>1.783053139858087</v>
       </c>
       <c r="G20" t="n">
-        <v>9.884461686310214</v>
+        <v>10.9894516866725</v>
       </c>
     </row>
     <row r="21">
@@ -1677,16 +1677,16 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4561307976544915</v>
+        <v>0.5260243442514434</v>
       </c>
       <c r="E21" t="n">
-        <v>2.873369848528209</v>
+        <v>2.682392430595852</v>
       </c>
       <c r="F21" t="n">
-        <v>1.848773668762279</v>
+        <v>1.817457667319941</v>
       </c>
       <c r="G21" t="n">
-        <v>11.48073204218273</v>
+        <v>11.53891491544293</v>
       </c>
     </row>
     <row r="22">
@@ -1704,16 +1704,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3372961985579841</v>
+        <v>0.2354062491361637</v>
       </c>
       <c r="E22" t="n">
-        <v>2.364636065600208</v>
+        <v>2.539919488341214</v>
       </c>
       <c r="F22" t="n">
-        <v>1.610978207194598</v>
+        <v>1.677204805743682</v>
       </c>
       <c r="G22" t="n">
-        <v>10.82854740139946</v>
+        <v>10.97802838586767</v>
       </c>
     </row>
     <row r="23">
@@ -1731,16 +1731,16 @@
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5493056142525183</v>
+        <v>0.3502839191916148</v>
       </c>
       <c r="E23" t="n">
-        <v>2.338853638891928</v>
+        <v>2.808172481564636</v>
       </c>
       <c r="F23" t="n">
-        <v>1.625921075521627</v>
+        <v>1.780126195886957</v>
       </c>
       <c r="G23" t="n">
-        <v>10.6114096453814</v>
+        <v>11.76795529205565</v>
       </c>
     </row>
     <row r="24">
@@ -1758,16 +1758,16 @@
         <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4486943163963046</v>
+        <v>0.2254935400602559</v>
       </c>
       <c r="E24" t="n">
-        <v>2.251754493728487</v>
+        <v>2.668930873055173</v>
       </c>
       <c r="F24" t="n">
-        <v>1.54304571975113</v>
+        <v>1.69773798668779</v>
       </c>
       <c r="G24" t="n">
-        <v>10.19277402867325</v>
+        <v>10.40031128031047</v>
       </c>
     </row>
     <row r="25">
@@ -1785,16 +1785,16 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4712146815302456</v>
+        <v>0.2079839702666535</v>
       </c>
       <c r="E25" t="n">
-        <v>2.452785459113523</v>
+        <v>3.001835257963587</v>
       </c>
       <c r="F25" t="n">
-        <v>1.526819039469361</v>
+        <v>1.763263546307023</v>
       </c>
       <c r="G25" t="n">
-        <v>9.489429275775372</v>
+        <v>10.1705784377731</v>
       </c>
     </row>
     <row r="26">
@@ -1812,16 +1812,16 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4578531165281005</v>
+        <v>0.5259873535128372</v>
       </c>
       <c r="E26" t="n">
-        <v>2.868816563185415</v>
+        <v>2.682497100255748</v>
       </c>
       <c r="F26" t="n">
-        <v>1.774570098910459</v>
+        <v>1.749588419302718</v>
       </c>
       <c r="G26" t="n">
-        <v>10.89009889050769</v>
+        <v>10.59420486042111</v>
       </c>
     </row>
   </sheetData>
@@ -1888,7 +1888,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16 19:28:16 UTC</t>
+          <t>2026-06-16 20:25:12 UTC</t>
         </is>
       </c>
       <c r="B2" t="n">
